--- a/User/MT/ForceDataBase.xlsx
+++ b/User/MT/ForceDataBase.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="100" sheetId="1" r:id="rId1"/>
+    <sheet name="1000" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
@@ -1278,4 +1279,9025 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B1001"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A1">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <f>EXP(LN(A1 + 0.009076778736745) / 1.46927)</f>
+        <v>4.0751887212009688E-2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A2">
+        <v>1E-3</v>
+      </c>
+      <c r="B2">
+        <f>EXP(LN(A2 + 0.009076778736745) / 1.46927)</f>
+        <v>4.3756300892787883E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A3">
+        <v>2E-3</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B66" si="0">EXP(LN(A3 + 0.009076778736745) / 1.46927)</f>
+        <v>4.6666804709746892E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A4">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>4.9494455968968676E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A5">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>5.22482088178901E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A6">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>5.4935443783974712E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A7">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>5.7562335938637403E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A8">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>6.0134118292967137E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A9">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>6.2655274890287618E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A10">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>6.512968536989823E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A11">
+        <v>0.01</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>6.7560735202198283E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A12">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>6.995140111470087E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A13">
+        <v>1.2E-2</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>7.2304318246738317E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A14">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>7.4621833619913369E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A15">
+        <v>1.4E-2</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>7.6906049204557944E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A16">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>7.9158856968376046E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A17">
+        <v>1.6E-2</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>8.1381967670015418E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A18">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>8.357693471808679E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A19">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="0"/>
+        <v>8.5745174097544397E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A20">
+        <v>1.9E-2</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="0"/>
+        <v>8.788798113250805E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A21">
+        <v>0.02</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="0"/>
+        <v>9.0006544682237344E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A22">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="0"/>
+        <v>9.2101959237813252E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A23">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="B23">
+        <f t="shared" si="0"/>
+        <v>9.417523528924282E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A24">
+        <v>2.3E-2</v>
+      </c>
+      <c r="B24">
+        <f t="shared" si="0"/>
+        <v>9.6227308257816835E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A25">
+        <v>2.4E-2</v>
+      </c>
+      <c r="B25">
+        <f t="shared" si="0"/>
+        <v>9.8259046230691302E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A26">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="B26">
+        <f t="shared" si="0"/>
+        <v>0.10027125668956052</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A27">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="B27">
+        <f t="shared" si="0"/>
+        <v>0.10226469238984047</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A28">
+        <v>2.7E-2</v>
+      </c>
+      <c r="B28">
+        <f t="shared" si="0"/>
+        <v>0.10424005651870238</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A29">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="B29">
+        <f t="shared" si="0"/>
+        <v>0.10619800723789677</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A30">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="B30">
+        <f t="shared" si="0"/>
+        <v>0.10813916169931366</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A31">
+        <v>0.03</v>
+      </c>
+      <c r="B31">
+        <f t="shared" si="0"/>
+        <v>0.11006409960667815</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A32">
+        <v>3.1E-2</v>
+      </c>
+      <c r="B32">
+        <f t="shared" si="0"/>
+        <v>0.11197336638495252</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A33">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="B33">
+        <f t="shared" si="0"/>
+        <v>0.11386747600933604</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A34">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="B34">
+        <f t="shared" si="0"/>
+        <v>0.11574691353779935</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A35">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="B35">
+        <f t="shared" si="0"/>
+        <v>0.11761213738450996</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A36">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="B36">
+        <f t="shared" si="0"/>
+        <v>0.11946358136604382</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A37">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="B37">
+        <f t="shared" si="0"/>
+        <v>0.12130165654771828</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A38">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="B38">
+        <f t="shared" si="0"/>
+        <v>0.12312675291356084</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A39">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="B39">
+        <f t="shared" si="0"/>
+        <v>0.12493924088021308</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A40">
+        <v>3.9E-2</v>
+      </c>
+      <c r="B40">
+        <f t="shared" si="0"/>
+        <v>0.12673947267235208</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A41">
+        <v>0.04</v>
+      </c>
+      <c r="B41">
+        <f t="shared" si="0"/>
+        <v>0.12852778357490668</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A42">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="B42">
+        <f t="shared" si="0"/>
+        <v>0.1303044930753848</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A43">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="B43">
+        <f t="shared" si="0"/>
+        <v>0.13206990590795162</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A44">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="B44">
+        <f t="shared" si="0"/>
+        <v>0.13382431300946279</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A45">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="B45">
+        <f t="shared" si="0"/>
+        <v>0.13556799239642162</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A46">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="B46">
+        <f t="shared" si="0"/>
+        <v>0.1373012099707637</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A47">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="B47">
+        <f t="shared" si="0"/>
+        <v>0.13902422026145242</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A48">
+        <v>4.7E-2</v>
+      </c>
+      <c r="B48">
+        <f t="shared" si="0"/>
+        <v>0.140737267108068</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A49">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="B49">
+        <f t="shared" si="0"/>
+        <v>0.1424405842918787</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A50">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="B50">
+        <f t="shared" si="0"/>
+        <v>0.14413439611927695</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A51">
+        <v>0.05</v>
+      </c>
+      <c r="B51">
+        <f t="shared" si="0"/>
+        <v>0.14581891796193189</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A52">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="B52">
+        <f t="shared" si="0"/>
+        <v>0.14749435675754657</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A53">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="B53">
+        <f t="shared" si="0"/>
+        <v>0.14916091147469987</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A54">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="B54">
+        <f t="shared" si="0"/>
+        <v>0.15081877354489293</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A55">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="B55">
+        <f t="shared" si="0"/>
+        <v>0.15246812726460482</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A56">
+        <v>5.5E-2</v>
+      </c>
+      <c r="B56">
+        <f t="shared" si="0"/>
+        <v>0.15410915016988033</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A57">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="B57">
+        <f t="shared" si="0"/>
+        <v>0.15574201338572452</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A58">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="B58">
+        <f t="shared" si="0"/>
+        <v>0.15736688195235995</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A59">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="B59">
+        <f t="shared" si="0"/>
+        <v>0.15898391513020377</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A60">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="B60">
+        <f t="shared" si="0"/>
+        <v>0.1605932666852494</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A61">
+        <v>0.06</v>
+      </c>
+      <c r="B61">
+        <f t="shared" si="0"/>
+        <v>0.16219508515638081</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A62">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="B62">
+        <f t="shared" si="0"/>
+        <v>0.16378951410600689</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A63">
+        <v>6.2E-2</v>
+      </c>
+      <c r="B63">
+        <f t="shared" si="0"/>
+        <v>0.16537669235528041</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A64">
+        <v>6.3E-2</v>
+      </c>
+      <c r="B64">
+        <f t="shared" si="0"/>
+        <v>0.16695675420505207</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A65">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="B65">
+        <f t="shared" si="0"/>
+        <v>0.16852982964361096</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A66">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="B66">
+        <f t="shared" si="0"/>
+        <v>0.17009604454217064</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A67">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="B67">
+        <f t="shared" ref="B67:B130" si="1">EXP(LN(A67 + 0.009076778736745) / 1.46927)</f>
+        <v>0.17165552083897989</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A68">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="B68">
+        <f t="shared" si="1"/>
+        <v>0.17320837671286157</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A69">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="B69">
+        <f t="shared" si="1"/>
+        <v>0.17475472674691836</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A70">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="B70">
+        <f t="shared" si="1"/>
+        <v>0.17629468208308158</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A71">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="B71">
+        <f t="shared" si="1"/>
+        <v>0.17782835056812729</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A72">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="B72">
+        <f t="shared" si="1"/>
+        <v>0.17935583689173068</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A73">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="B73">
+        <f t="shared" si="1"/>
+        <v>0.18087724271708844</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A74">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="B74">
+        <f t="shared" si="1"/>
+        <v>0.18239266680459451</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A75">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="B75">
+        <f t="shared" si="1"/>
+        <v>0.18390220512901975</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A76">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="B76">
+        <f t="shared" si="1"/>
+        <v>0.18540595099060941</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A77">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="B77">
+        <f t="shared" si="1"/>
+        <v>0.186903995120484</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A78">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="B78">
+        <f t="shared" si="1"/>
+        <v>0.18839642578069765</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A79">
+        <v>7.8E-2</v>
+      </c>
+      <c r="B79">
+        <f t="shared" si="1"/>
+        <v>0.18988332885928474</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A80">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="B80">
+        <f t="shared" si="1"/>
+        <v>0.19136478796059994</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A81">
+        <v>0.08</v>
+      </c>
+      <c r="B81">
+        <f t="shared" si="1"/>
+        <v>0.19284088449123513</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A82">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="B82">
+        <f t="shared" si="1"/>
+        <v>0.19431169774177748</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A83">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="B83">
+        <f t="shared" si="1"/>
+        <v>0.19577730496465365</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A84">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="B84">
+        <f t="shared" si="1"/>
+        <v>0.19723778144828799</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A85">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="B85">
+        <f t="shared" si="1"/>
+        <v>0.198693200587788</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A86">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="B86">
+        <f t="shared" si="1"/>
+        <v>0.20014363395235463</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A87">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="B87">
+        <f t="shared" si="1"/>
+        <v>0.20158915134960229</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A88">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="B88">
+        <f t="shared" si="1"/>
+        <v>0.20302982088696228</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A89">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="B89">
+        <f t="shared" si="1"/>
+        <v>0.20446570903032885</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A90">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="B90">
+        <f t="shared" si="1"/>
+        <v>0.2058968806601007</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A91">
+        <v>0.09</v>
+      </c>
+      <c r="B91">
+        <f t="shared" si="1"/>
+        <v>0.20732339912475797</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A92">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="B92">
+        <f t="shared" si="1"/>
+        <v>0.20874532629210713</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A93">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="B93">
+        <f t="shared" si="1"/>
+        <v>0.2101627225983172</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A94">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="B94">
+        <f t="shared" si="1"/>
+        <v>0.21157564709486368</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A95">
+        <v>9.4E-2</v>
+      </c>
+      <c r="B95">
+        <f t="shared" si="1"/>
+        <v>0.21298415749348953</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A96">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="B96">
+        <f t="shared" si="1"/>
+        <v>0.21438831020928389</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A97">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="B97">
+        <f t="shared" si="1"/>
+        <v>0.21578816040197668</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A98">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="B98">
+        <f t="shared" si="1"/>
+        <v>0.21718376201553705</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A99">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="B99">
+        <f t="shared" si="1"/>
+        <v>0.21857516781616254</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A100">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="B100">
+        <f t="shared" si="1"/>
+        <v>0.21996242942873762</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A101">
+        <v>0.1</v>
+      </c>
+      <c r="B101">
+        <f t="shared" si="1"/>
+        <v>0.22134559737183729</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A102">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="B102">
+        <f t="shared" si="1"/>
+        <v>0.22272472109134647</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A103">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="B103">
+        <f t="shared" si="1"/>
+        <v>0.22409984899276178</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A104">
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="B104">
+        <f t="shared" si="1"/>
+        <v>0.22547102847223946</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A105">
+        <v>0.104</v>
+      </c>
+      <c r="B105">
+        <f t="shared" si="1"/>
+        <v>0.22683830594644785</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A106">
+        <v>0.105</v>
+      </c>
+      <c r="B106">
+        <f t="shared" si="1"/>
+        <v>0.2282017268812811</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A107">
+        <v>0.106</v>
+      </c>
+      <c r="B107">
+        <f t="shared" si="1"/>
+        <v>0.22956133581948762</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A108">
+        <v>0.107</v>
+      </c>
+      <c r="B108">
+        <f t="shared" si="1"/>
+        <v>0.23091717640726242</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A109">
+        <v>0.108</v>
+      </c>
+      <c r="B109">
+        <f t="shared" si="1"/>
+        <v>0.23226929141985125</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A110">
+        <v>0.109</v>
+      </c>
+      <c r="B110">
+        <f t="shared" si="1"/>
+        <v>0.2336177227862116</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A111">
+        <v>0.11</v>
+      </c>
+      <c r="B111">
+        <f t="shared" si="1"/>
+        <v>0.23496251161277232</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A112">
+        <v>0.111</v>
+      </c>
+      <c r="B112">
+        <f t="shared" si="1"/>
+        <v>0.23630369820633301</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A113">
+        <v>0.112</v>
+      </c>
+      <c r="B113">
+        <f t="shared" si="1"/>
+        <v>0.23764132209614036</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A114">
+        <v>0.113</v>
+      </c>
+      <c r="B114">
+        <f t="shared" si="1"/>
+        <v>0.23897542205517805</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A115">
+        <v>0.114</v>
+      </c>
+      <c r="B115">
+        <f t="shared" si="1"/>
+        <v>0.24030603612070411</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A116">
+        <v>0.115</v>
+      </c>
+      <c r="B116">
+        <f t="shared" si="1"/>
+        <v>0.24163320161406893</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A117">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="B117">
+        <f t="shared" si="1"/>
+        <v>0.24295695515984356</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A118">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="B118">
+        <f t="shared" si="1"/>
+        <v>0.24427733270428853</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A119">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="B119">
+        <f t="shared" si="1"/>
+        <v>0.24559436953319116</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A120">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="B120">
+        <f t="shared" si="1"/>
+        <v>0.24690810028909621</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A121">
+        <v>0.12</v>
+      </c>
+      <c r="B121">
+        <f t="shared" si="1"/>
+        <v>0.24821855898795736</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A122">
+        <v>0.121</v>
+      </c>
+      <c r="B122">
+        <f t="shared" si="1"/>
+        <v>0.24952577903523121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A123">
+        <v>0.122</v>
+      </c>
+      <c r="B123">
+        <f t="shared" si="1"/>
+        <v>0.25082979324143789</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A124">
+        <v>0.123</v>
+      </c>
+      <c r="B124">
+        <f t="shared" si="1"/>
+        <v>0.25213063383720974</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A125">
+        <v>0.124</v>
+      </c>
+      <c r="B125">
+        <f t="shared" si="1"/>
+        <v>0.25342833248784763</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A126">
+        <v>0.125</v>
+      </c>
+      <c r="B126">
+        <f t="shared" si="1"/>
+        <v>0.25472292030740618</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A127">
+        <v>0.126</v>
+      </c>
+      <c r="B127">
+        <f t="shared" si="1"/>
+        <v>0.25601442787232515</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A128">
+        <v>0.127</v>
+      </c>
+      <c r="B128">
+        <f t="shared" si="1"/>
+        <v>0.25730288523462613</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A129">
+        <v>0.128</v>
+      </c>
+      <c r="B129">
+        <f t="shared" si="1"/>
+        <v>0.25858832193468978</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A130">
+        <v>0.129</v>
+      </c>
+      <c r="B130">
+        <f t="shared" si="1"/>
+        <v>0.25987076701363193</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A131">
+        <v>0.13</v>
+      </c>
+      <c r="B131">
+        <f t="shared" ref="B131:B194" si="2">EXP(LN(A131 + 0.009076778736745) / 1.46927)</f>
+        <v>0.26115024902529232</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A132">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="B132">
+        <f t="shared" si="2"/>
+        <v>0.26242679604785174</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A133">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="B133">
+        <f t="shared" si="2"/>
+        <v>0.26370043569509088</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A134">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="B134">
+        <f t="shared" si="2"/>
+        <v>0.26497119512730555</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A135">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="B135">
+        <f t="shared" si="2"/>
+        <v>0.2662391010618898</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A136">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="B136">
+        <f t="shared" si="2"/>
+        <v>0.26750417978360019</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A137">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="B137">
+        <f t="shared" si="2"/>
+        <v>0.26876645715451269</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A138">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="B138">
+        <f t="shared" si="2"/>
+        <v>0.270025958623683</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A139">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="B139">
+        <f t="shared" si="2"/>
+        <v>0.27128270923652242</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A140">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="B140">
+        <f t="shared" si="2"/>
+        <v>0.27253673364389769</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A141">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="B141">
+        <f t="shared" si="2"/>
+        <v>0.27378805611096618</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A142">
+        <v>0.14099999999999999</v>
+      </c>
+      <c r="B142">
+        <f t="shared" si="2"/>
+        <v>0.2750367005257553</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A143">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="B143">
+        <f t="shared" si="2"/>
+        <v>0.27628269040749542</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A144">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="B144">
+        <f t="shared" si="2"/>
+        <v>0.277526048914714</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A145">
+        <v>0.14399999999999999</v>
+      </c>
+      <c r="B145">
+        <f t="shared" si="2"/>
+        <v>0.27876679885310135</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A146">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="B146">
+        <f t="shared" si="2"/>
+        <v>0.28000496268315322</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A147">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="B147">
+        <f t="shared" si="2"/>
+        <v>0.28124056252760066</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A148">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="B148">
+        <f t="shared" si="2"/>
+        <v>0.28247362017863231</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A149">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="B149">
+        <f t="shared" si="2"/>
+        <v>0.28370415710491709</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A150">
+        <v>0.14899999999999999</v>
+      </c>
+      <c r="B150">
+        <f t="shared" si="2"/>
+        <v>0.28493219445843448</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A151">
+        <v>0.15</v>
+      </c>
+      <c r="B151">
+        <f t="shared" si="2"/>
+        <v>0.28615775308111779</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A152">
+        <v>0.151</v>
+      </c>
+      <c r="B152">
+        <f t="shared" si="2"/>
+        <v>0.28738085351131759</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A153">
+        <v>0.152</v>
+      </c>
+      <c r="B153">
+        <f t="shared" si="2"/>
+        <v>0.28860151599009032</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A154">
+        <v>0.153</v>
+      </c>
+      <c r="B154">
+        <f t="shared" si="2"/>
+        <v>0.2898197604673195</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A155">
+        <v>0.154</v>
+      </c>
+      <c r="B155">
+        <f t="shared" si="2"/>
+        <v>0.29103560660767286</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A156">
+        <v>0.155</v>
+      </c>
+      <c r="B156">
+        <f t="shared" si="2"/>
+        <v>0.29224907379640247</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A157">
+        <v>0.156</v>
+      </c>
+      <c r="B157">
+        <f t="shared" si="2"/>
+        <v>0.29346018114499206</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A158">
+        <v>0.157</v>
+      </c>
+      <c r="B158">
+        <f t="shared" si="2"/>
+        <v>0.29466894749665695</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A159">
+        <v>0.158</v>
+      </c>
+      <c r="B159">
+        <f t="shared" si="2"/>
+        <v>0.29587539143170061</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A160">
+        <v>0.159</v>
+      </c>
+      <c r="B160">
+        <f t="shared" si="2"/>
+        <v>0.29707953127273368</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A161">
+        <v>0.16</v>
+      </c>
+      <c r="B161">
+        <f t="shared" si="2"/>
+        <v>0.29828138508975799</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A162">
+        <v>0.161</v>
+      </c>
+      <c r="B162">
+        <f t="shared" si="2"/>
+        <v>0.29948097070512159</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A163">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="B163">
+        <f t="shared" si="2"/>
+        <v>0.30067830569834764</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A164">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="B164">
+        <f t="shared" si="2"/>
+        <v>0.30187340741084179</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A165">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="B165">
+        <f t="shared" si="2"/>
+        <v>0.30306629295048115</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A166">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="B166">
+        <f t="shared" si="2"/>
+        <v>0.30425697919608924</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A167">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="B167">
+        <f t="shared" si="2"/>
+        <v>0.30544548280179951</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A168">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="B168">
+        <f t="shared" si="2"/>
+        <v>0.30663182020131191</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A169">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="B169">
+        <f t="shared" si="2"/>
+        <v>0.30781600761204458</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A170">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="B170">
+        <f t="shared" si="2"/>
+        <v>0.30899806103918459</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A171">
+        <v>0.17</v>
+      </c>
+      <c r="B171">
+        <f t="shared" si="2"/>
+        <v>0.31017799627964071</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A172">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="B172">
+        <f t="shared" si="2"/>
+        <v>0.31135582892590047</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A173">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="B173">
+        <f t="shared" si="2"/>
+        <v>0.31253157436979501</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A174">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="B174">
+        <f t="shared" si="2"/>
+        <v>0.31370524780617465</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A175">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="B175">
+        <f t="shared" si="2"/>
+        <v>0.31487686423649625</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A176">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="B176">
+        <f t="shared" si="2"/>
+        <v>0.31604643847232727</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A177">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="B177">
+        <f t="shared" si="2"/>
+        <v>0.31721398513876664</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A178">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="B178">
+        <f t="shared" si="2"/>
+        <v>0.31837951867778658</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A179">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="B179">
+        <f t="shared" si="2"/>
+        <v>0.31954305335149635</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A180">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="B180">
+        <f t="shared" si="2"/>
+        <v>0.32070460324533134</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A181">
+        <v>0.18</v>
+      </c>
+      <c r="B181">
+        <f t="shared" si="2"/>
+        <v>0.32186418227116809</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A182">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="B182">
+        <f t="shared" si="2"/>
+        <v>0.32302180417036941</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A183">
+        <v>0.182</v>
+      </c>
+      <c r="B183">
+        <f t="shared" si="2"/>
+        <v>0.32417748251675887</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A184">
+        <v>0.183</v>
+      </c>
+      <c r="B184">
+        <f t="shared" si="2"/>
+        <v>0.32533123071952974</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A185">
+        <v>0.184</v>
+      </c>
+      <c r="B185">
+        <f t="shared" si="2"/>
+        <v>0.32648306202608729</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A186">
+        <v>0.185</v>
+      </c>
+      <c r="B186">
+        <f t="shared" si="2"/>
+        <v>0.32763298952482778</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A187">
+        <v>0.186</v>
+      </c>
+      <c r="B187">
+        <f t="shared" si="2"/>
+        <v>0.3287810261478567</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A188">
+        <v>0.187</v>
+      </c>
+      <c r="B188">
+        <f t="shared" si="2"/>
+        <v>0.32992718467364496</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A189">
+        <v>0.188</v>
+      </c>
+      <c r="B189">
+        <f t="shared" si="2"/>
+        <v>0.33107147772962858</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A190">
+        <v>0.189</v>
+      </c>
+      <c r="B190">
+        <f t="shared" si="2"/>
+        <v>0.33221391779475024</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A191">
+        <v>0.19</v>
+      </c>
+      <c r="B191">
+        <f t="shared" si="2"/>
+        <v>0.33335451720194581</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A192">
+        <v>0.191</v>
+      </c>
+      <c r="B192">
+        <f t="shared" si="2"/>
+        <v>0.33449328814057683</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A193">
+        <v>0.192</v>
+      </c>
+      <c r="B193">
+        <f t="shared" si="2"/>
+        <v>0.3356302426588107</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A194">
+        <v>0.193</v>
+      </c>
+      <c r="B194">
+        <f t="shared" si="2"/>
+        <v>0.33676539266594996</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A195">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="B195">
+        <f t="shared" ref="B195:B258" si="3">EXP(LN(A195 + 0.009076778736745) / 1.46927)</f>
+        <v>0.33789874993471108</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A196">
+        <v>0.19500000000000001</v>
+      </c>
+      <c r="B196">
+        <f t="shared" si="3"/>
+        <v>0.33903032610345557</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A197">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="B197">
+        <f t="shared" si="3"/>
+        <v>0.34016013267837403</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A198">
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="B198">
+        <f t="shared" si="3"/>
+        <v>0.34128818103562281</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A199">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="B199">
+        <f t="shared" si="3"/>
+        <v>0.34241448242341826</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A200">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="B200">
+        <f t="shared" si="3"/>
+        <v>0.34353904796408485</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A201">
+        <v>0.2</v>
+      </c>
+      <c r="B201">
+        <f t="shared" si="3"/>
+        <v>0.34466188865606279</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A202">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="B202">
+        <f t="shared" si="3"/>
+        <v>0.34578301537587303</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A203">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="B203">
+        <f t="shared" si="3"/>
+        <v>0.34690243888004207</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A204">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="B204">
+        <f t="shared" si="3"/>
+        <v>0.34802016980698819</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A205">
+        <v>0.20399999999999999</v>
+      </c>
+      <c r="B205">
+        <f t="shared" si="3"/>
+        <v>0.34913621867886807</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A206">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="B206">
+        <f t="shared" si="3"/>
+        <v>0.35025059590338709</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A207">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="B207">
+        <f t="shared" si="3"/>
+        <v>0.35136331177557223</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A208">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="B208">
+        <f t="shared" si="3"/>
+        <v>0.35247437647951024</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A209">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="B209">
+        <f t="shared" si="3"/>
+        <v>0.35358380009005042</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A210">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="B210">
+        <f t="shared" si="3"/>
+        <v>0.35469159257447402</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A211">
+        <v>0.21</v>
+      </c>
+      <c r="B211">
+        <f t="shared" si="3"/>
+        <v>0.35579776379413003</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A212">
+        <v>0.21099999999999999</v>
+      </c>
+      <c r="B212">
+        <f t="shared" si="3"/>
+        <v>0.35690232350603934</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A213">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="B213">
+        <f t="shared" si="3"/>
+        <v>0.35800528136446724</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A214">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="B214">
+        <f t="shared" si="3"/>
+        <v>0.35910664692246497</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A215">
+        <v>0.214</v>
+      </c>
+      <c r="B215">
+        <f t="shared" si="3"/>
+        <v>0.36020642963338162</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A216">
+        <v>0.215</v>
+      </c>
+      <c r="B216">
+        <f t="shared" si="3"/>
+        <v>0.36130463885234659</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A217">
+        <v>0.216</v>
+      </c>
+      <c r="B217">
+        <f t="shared" si="3"/>
+        <v>0.36240128383772369</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A218">
+        <v>0.217</v>
+      </c>
+      <c r="B218">
+        <f t="shared" si="3"/>
+        <v>0.36349637375253713</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A219">
+        <v>0.218</v>
+      </c>
+      <c r="B219">
+        <f t="shared" si="3"/>
+        <v>0.36458991766587029</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A220">
+        <v>0.219</v>
+      </c>
+      <c r="B220">
+        <f t="shared" si="3"/>
+        <v>0.36568192455423815</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A221">
+        <v>0.22</v>
+      </c>
+      <c r="B221">
+        <f t="shared" si="3"/>
+        <v>0.36677240330293348</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A222">
+        <v>0.221</v>
+      </c>
+      <c r="B222">
+        <f t="shared" si="3"/>
+        <v>0.36786136270734798</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A223">
+        <v>0.222</v>
+      </c>
+      <c r="B223">
+        <f t="shared" si="3"/>
+        <v>0.368948811474268</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A224">
+        <v>0.223</v>
+      </c>
+      <c r="B224">
+        <f t="shared" si="3"/>
+        <v>0.37003475822314702</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A225">
+        <v>0.224</v>
+      </c>
+      <c r="B225">
+        <f t="shared" si="3"/>
+        <v>0.37111921148735344</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A226">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="B226">
+        <f t="shared" si="3"/>
+        <v>0.3722021797153961</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A227">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="B227">
+        <f t="shared" si="3"/>
+        <v>0.37328367127212658</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A228">
+        <v>0.22700000000000001</v>
+      </c>
+      <c r="B228">
+        <f t="shared" si="3"/>
+        <v>0.3743636944399199</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A229">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="B229">
+        <f t="shared" si="3"/>
+        <v>0.37544225741983328</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A230">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="B230">
+        <f t="shared" si="3"/>
+        <v>0.37651936833274402</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A231">
+        <v>0.23</v>
+      </c>
+      <c r="B231">
+        <f t="shared" si="3"/>
+        <v>0.37759503522046667</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A232">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="B232">
+        <f t="shared" si="3"/>
+        <v>0.37866926604684992</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A233">
+        <v>0.23200000000000001</v>
+      </c>
+      <c r="B233">
+        <f t="shared" si="3"/>
+        <v>0.37974206869885407</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A234">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="B234">
+        <f t="shared" si="3"/>
+        <v>0.38081345098760894</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A235">
+        <v>0.23400000000000001</v>
+      </c>
+      <c r="B235">
+        <f t="shared" si="3"/>
+        <v>0.3818834206494528</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A236">
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="B236">
+        <f t="shared" si="3"/>
+        <v>0.38295198534695341</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A237">
+        <v>0.23599999999999999</v>
+      </c>
+      <c r="B237">
+        <f t="shared" si="3"/>
+        <v>0.38401915266991044</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A238">
+        <v>0.23699999999999999</v>
+      </c>
+      <c r="B238">
+        <f t="shared" si="3"/>
+        <v>0.38508493013634015</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A239">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="B239">
+        <f t="shared" si="3"/>
+        <v>0.38614932519344369</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A240">
+        <v>0.23899999999999999</v>
+      </c>
+      <c r="B240">
+        <f t="shared" si="3"/>
+        <v>0.38721234521855741</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A241">
+        <v>0.24</v>
+      </c>
+      <c r="B241">
+        <f t="shared" si="3"/>
+        <v>0.38827399752008712</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A242">
+        <v>0.24099999999999999</v>
+      </c>
+      <c r="B242">
+        <f t="shared" si="3"/>
+        <v>0.38933428933842645</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A243">
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="B243">
+        <f t="shared" si="3"/>
+        <v>0.39039322784685865</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A244">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="B244">
+        <f t="shared" si="3"/>
+        <v>0.39145082015244348</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A245">
+        <v>0.24399999999999999</v>
+      </c>
+      <c r="B245">
+        <f t="shared" si="3"/>
+        <v>0.39250707329688861</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A246">
+        <v>0.245</v>
+      </c>
+      <c r="B246">
+        <f t="shared" si="3"/>
+        <v>0.39356199425740662</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A247">
+        <v>0.246</v>
+      </c>
+      <c r="B247">
+        <f t="shared" si="3"/>
+        <v>0.39461558994755641</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A248">
+        <v>0.247</v>
+      </c>
+      <c r="B248">
+        <f t="shared" si="3"/>
+        <v>0.39566786721807168</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A249">
+        <v>0.248</v>
+      </c>
+      <c r="B249">
+        <f t="shared" si="3"/>
+        <v>0.39671883285767429</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A250">
+        <v>0.249</v>
+      </c>
+      <c r="B250">
+        <f t="shared" si="3"/>
+        <v>0.39776849359387484</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A251">
+        <v>0.25</v>
+      </c>
+      <c r="B251">
+        <f t="shared" si="3"/>
+        <v>0.39881685609375939</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A252">
+        <v>0.251</v>
+      </c>
+      <c r="B252">
+        <f t="shared" si="3"/>
+        <v>0.39986392696476303</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A253">
+        <v>0.252</v>
+      </c>
+      <c r="B253">
+        <f t="shared" si="3"/>
+        <v>0.40090971275543097</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A254">
+        <v>0.253</v>
+      </c>
+      <c r="B254">
+        <f t="shared" si="3"/>
+        <v>0.40195421995616648</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A255">
+        <v>0.254</v>
+      </c>
+      <c r="B255">
+        <f t="shared" si="3"/>
+        <v>0.40299745499996747</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A256">
+        <v>0.255</v>
+      </c>
+      <c r="B256">
+        <f t="shared" si="3"/>
+        <v>0.4040394242631497</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A257">
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="B257">
+        <f t="shared" si="3"/>
+        <v>0.40508013406605919</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A258">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="B258">
+        <f t="shared" si="3"/>
+        <v>0.40611959067377279</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A259">
+        <v>0.25800000000000001</v>
+      </c>
+      <c r="B259">
+        <f t="shared" ref="B259:B322" si="4">EXP(LN(A259 + 0.009076778736745) / 1.46927)</f>
+        <v>0.40715780029678683</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A260">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="B260">
+        <f t="shared" si="4"/>
+        <v>0.40819476909169561</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A261">
+        <v>0.26</v>
+      </c>
+      <c r="B261">
+        <f t="shared" si="4"/>
+        <v>0.40923050316185799</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A262">
+        <v>0.26100000000000001</v>
+      </c>
+      <c r="B262">
+        <f t="shared" si="4"/>
+        <v>0.41026500855805398</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A263">
+        <v>0.26200000000000001</v>
+      </c>
+      <c r="B263">
+        <f t="shared" si="4"/>
+        <v>0.4112982912791307</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A264">
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="B264">
+        <f t="shared" si="4"/>
+        <v>0.4123303572726375</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A265">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="B265">
+        <f t="shared" si="4"/>
+        <v>0.41336121243545182</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A266">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="B266">
+        <f t="shared" si="4"/>
+        <v>0.41439086261439478</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A267">
+        <v>0.26600000000000001</v>
+      </c>
+      <c r="B267">
+        <f t="shared" si="4"/>
+        <v>0.41541931360683676</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A268">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="B268">
+        <f t="shared" si="4"/>
+        <v>0.41644657116129402</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A269">
+        <v>0.26800000000000002</v>
+      </c>
+      <c r="B269">
+        <f t="shared" si="4"/>
+        <v>0.41747264097801584</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A270">
+        <v>0.26900000000000002</v>
+      </c>
+      <c r="B270">
+        <f t="shared" si="4"/>
+        <v>0.41849752870956236</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A271">
+        <v>0.27</v>
+      </c>
+      <c r="B271">
+        <f t="shared" si="4"/>
+        <v>0.41952123996137319</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A272">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="B272">
+        <f t="shared" si="4"/>
+        <v>0.42054378029232825</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A273">
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="B273">
+        <f t="shared" si="4"/>
+        <v>0.42156515521529841</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A274">
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="B274">
+        <f t="shared" si="4"/>
+        <v>0.42258537019768933</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A275">
+        <v>0.27400000000000002</v>
+      </c>
+      <c r="B275">
+        <f t="shared" si="4"/>
+        <v>0.42360443066197573</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A276">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="B276">
+        <f t="shared" si="4"/>
+        <v>0.42462234198622806</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A277">
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="B277">
+        <f t="shared" si="4"/>
+        <v>0.42563910950463102</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A278">
+        <v>0.27700000000000002</v>
+      </c>
+      <c r="B278">
+        <f t="shared" si="4"/>
+        <v>0.42665473850799446</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A279">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="B279">
+        <f t="shared" si="4"/>
+        <v>0.42766923424425607</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A280">
+        <v>0.27900000000000003</v>
+      </c>
+      <c r="B280">
+        <f t="shared" si="4"/>
+        <v>0.42868260191897745</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A281">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="B281">
+        <f t="shared" si="4"/>
+        <v>0.42969484669583102</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A282">
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="B282">
+        <f t="shared" si="4"/>
+        <v>0.43070597369708208</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A283">
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="B283">
+        <f t="shared" si="4"/>
+        <v>0.43171598800406125</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A284">
+        <v>0.28299999999999997</v>
+      </c>
+      <c r="B284">
+        <f t="shared" si="4"/>
+        <v>0.43272489465763181</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A285">
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="B285">
+        <f t="shared" si="4"/>
+        <v>0.43373269865864916</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A286">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="B286">
+        <f t="shared" si="4"/>
+        <v>0.43473940496841312</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A287">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="B287">
+        <f t="shared" si="4"/>
+        <v>0.43574501850911512</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A288">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="B288">
+        <f t="shared" si="4"/>
+        <v>0.43674954416427725</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A289">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="B289">
+        <f t="shared" si="4"/>
+        <v>0.43775298677918567</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A290">
+        <v>0.28899999999999998</v>
+      </c>
+      <c r="B290">
+        <f t="shared" si="4"/>
+        <v>0.43875535116131803</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A291">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="B291">
+        <f t="shared" si="4"/>
+        <v>0.43975664208076359</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A292">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="B292">
+        <f t="shared" si="4"/>
+        <v>0.44075686427063848</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A293">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="B293">
+        <f t="shared" si="4"/>
+        <v>0.44175602242749434</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A294">
+        <v>0.29299999999999998</v>
+      </c>
+      <c r="B294">
+        <f t="shared" si="4"/>
+        <v>0.4427541212117212</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A295">
+        <v>0.29399999999999998</v>
+      </c>
+      <c r="B295">
+        <f t="shared" si="4"/>
+        <v>0.44375116524794456</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A296">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="B296">
+        <f t="shared" si="4"/>
+        <v>0.44474715912541724</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A297">
+        <v>0.29599999999999999</v>
+      </c>
+      <c r="B297">
+        <f t="shared" si="4"/>
+        <v>0.44574210739840475</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A298">
+        <v>0.29699999999999999</v>
+      </c>
+      <c r="B298">
+        <f t="shared" si="4"/>
+        <v>0.44673601458656625</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A299">
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="B299">
+        <f t="shared" si="4"/>
+        <v>0.44772888517532949</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A300">
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="B300">
+        <f t="shared" si="4"/>
+        <v>0.44872072361626075</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A301">
+        <v>0.3</v>
+      </c>
+      <c r="B301">
+        <f t="shared" si="4"/>
+        <v>0.44971153432742916</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A302">
+        <v>0.30099999999999999</v>
+      </c>
+      <c r="B302">
+        <f t="shared" si="4"/>
+        <v>0.45070132169376675</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A303">
+        <v>0.30199999999999999</v>
+      </c>
+      <c r="B303">
+        <f t="shared" si="4"/>
+        <v>0.45169009006742256</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A304">
+        <v>0.30299999999999999</v>
+      </c>
+      <c r="B304">
+        <f t="shared" si="4"/>
+        <v>0.45267784376811265</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A305">
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="B305">
+        <f t="shared" si="4"/>
+        <v>0.45366458708346458</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A306">
+        <v>0.30499999999999999</v>
+      </c>
+      <c r="B306">
+        <f t="shared" si="4"/>
+        <v>0.45465032426935781</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A307">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="B307">
+        <f t="shared" si="4"/>
+        <v>0.45563505955025863</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A308">
+        <v>0.307</v>
+      </c>
+      <c r="B308">
+        <f t="shared" si="4"/>
+        <v>0.45661879711955122</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A309">
+        <v>0.308</v>
+      </c>
+      <c r="B309">
+        <f t="shared" si="4"/>
+        <v>0.45760154113986412</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A310">
+        <v>0.309</v>
+      </c>
+      <c r="B310">
+        <f t="shared" si="4"/>
+        <v>0.45858329574339135</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A311">
+        <v>0.31</v>
+      </c>
+      <c r="B311">
+        <f t="shared" si="4"/>
+        <v>0.4595640650322107</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A312">
+        <v>0.311</v>
+      </c>
+      <c r="B312">
+        <f t="shared" si="4"/>
+        <v>0.46054385307859613</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A313">
+        <v>0.312</v>
+      </c>
+      <c r="B313">
+        <f t="shared" si="4"/>
+        <v>0.46152266392532726</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A314">
+        <v>0.313</v>
+      </c>
+      <c r="B314">
+        <f t="shared" si="4"/>
+        <v>0.46250050158599387</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A315">
+        <v>0.314</v>
+      </c>
+      <c r="B315">
+        <f t="shared" si="4"/>
+        <v>0.46347737004529654</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A316">
+        <v>0.315</v>
+      </c>
+      <c r="B316">
+        <f t="shared" si="4"/>
+        <v>0.46445327325934366</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A317">
+        <v>0.316</v>
+      </c>
+      <c r="B317">
+        <f t="shared" si="4"/>
+        <v>0.46542821515594357</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A318">
+        <v>0.317</v>
+      </c>
+      <c r="B318">
+        <f t="shared" si="4"/>
+        <v>0.46640219963489404</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A319">
+        <v>0.318</v>
+      </c>
+      <c r="B319">
+        <f t="shared" si="4"/>
+        <v>0.4673752305682668</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A320">
+        <v>0.31900000000000001</v>
+      </c>
+      <c r="B320">
+        <f t="shared" si="4"/>
+        <v>0.46834731180068906</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A321">
+        <v>0.32</v>
+      </c>
+      <c r="B321">
+        <f t="shared" si="4"/>
+        <v>0.46931844714962068</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A322">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="B322">
+        <f t="shared" si="4"/>
+        <v>0.4702886404056289</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A323">
+        <v>0.32200000000000001</v>
+      </c>
+      <c r="B323">
+        <f t="shared" ref="B323:B386" si="5">EXP(LN(A323 + 0.009076778736745) / 1.46927)</f>
+        <v>0.47125789533265727</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A324">
+        <v>0.32300000000000001</v>
+      </c>
+      <c r="B324">
+        <f t="shared" si="5"/>
+        <v>0.47222621566829409</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A325">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="B325">
+        <f t="shared" si="5"/>
+        <v>0.47319360512403452</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A326">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="B326">
+        <f t="shared" si="5"/>
+        <v>0.47416006738554084</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A327">
+        <v>0.32600000000000001</v>
+      </c>
+      <c r="B327">
+        <f t="shared" si="5"/>
+        <v>0.47512560611289917</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A328">
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="B328">
+        <f t="shared" si="5"/>
+        <v>0.47609022494087266</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A329">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="B329">
+        <f t="shared" si="5"/>
+        <v>0.47705392747915137</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A330">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="B330">
+        <f t="shared" si="5"/>
+        <v>0.47801671731259893</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A331">
+        <v>0.33</v>
+      </c>
+      <c r="B331">
+        <f t="shared" si="5"/>
+        <v>0.47897859800149678</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A332">
+        <v>0.33100000000000002</v>
+      </c>
+      <c r="B332">
+        <f t="shared" si="5"/>
+        <v>0.47993957308178387</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A333">
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="B333">
+        <f t="shared" si="5"/>
+        <v>0.48089964606529495</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A334">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="B334">
+        <f t="shared" si="5"/>
+        <v>0.4818588204399944</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A335">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="B335">
+        <f t="shared" si="5"/>
+        <v>0.48281709967020814</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A336">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="B336">
+        <f t="shared" si="5"/>
+        <v>0.48377448719685229</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A337">
+        <v>0.33600000000000002</v>
+      </c>
+      <c r="B337">
+        <f t="shared" si="5"/>
+        <v>0.48473098643765833</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A338">
+        <v>0.33700000000000002</v>
+      </c>
+      <c r="B338">
+        <f t="shared" si="5"/>
+        <v>0.48568660078739678</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A339">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="B339">
+        <f t="shared" si="5"/>
+        <v>0.48664133361809697</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A340">
+        <v>0.33900000000000002</v>
+      </c>
+      <c r="B340">
+        <f t="shared" si="5"/>
+        <v>0.48759518827926412</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A341">
+        <v>0.34</v>
+      </c>
+      <c r="B341">
+        <f t="shared" si="5"/>
+        <v>0.4885481680980947</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A342">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="B342">
+        <f t="shared" si="5"/>
+        <v>0.48950027637968796</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A343">
+        <v>0.34200000000000003</v>
+      </c>
+      <c r="B343">
+        <f t="shared" si="5"/>
+        <v>0.49045151640725571</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A344">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="B344">
+        <f t="shared" si="5"/>
+        <v>0.49140189144232871</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A345">
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="B345">
+        <f t="shared" si="5"/>
+        <v>0.49235140472496142</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A346">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="B346">
+        <f t="shared" si="5"/>
+        <v>0.49330005947393368</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A347">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="B347">
+        <f t="shared" si="5"/>
+        <v>0.49424785888695022</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A348">
+        <v>0.34699999999999998</v>
+      </c>
+      <c r="B348">
+        <f t="shared" si="5"/>
+        <v>0.49519480614083694</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A349">
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="B349">
+        <f t="shared" si="5"/>
+        <v>0.4961409043917363</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A350">
+        <v>0.34899999999999998</v>
+      </c>
+      <c r="B350">
+        <f t="shared" si="5"/>
+        <v>0.49708615677529916</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A351">
+        <v>0.35</v>
+      </c>
+      <c r="B351">
+        <f t="shared" si="5"/>
+        <v>0.49803056640687449</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A352">
+        <v>0.35099999999999998</v>
+      </c>
+      <c r="B352">
+        <f t="shared" si="5"/>
+        <v>0.49897413638169724</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A353">
+        <v>0.35199999999999998</v>
+      </c>
+      <c r="B353">
+        <f t="shared" si="5"/>
+        <v>0.49991686977507332</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A354">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="B354">
+        <f t="shared" si="5"/>
+        <v>0.50085876964256337</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A355">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="B355">
+        <f t="shared" si="5"/>
+        <v>0.50179983902016279</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A356">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="B356">
+        <f t="shared" si="5"/>
+        <v>0.50274008092448164</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A357">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="B357">
+        <f t="shared" si="5"/>
+        <v>0.50367949835292003</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A358">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="B358">
+        <f t="shared" si="5"/>
+        <v>0.50461809428384385</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A359">
+        <v>0.35799999999999998</v>
+      </c>
+      <c r="B359">
+        <f t="shared" si="5"/>
+        <v>0.50555587167675664</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A360">
+        <v>0.35899999999999999</v>
+      </c>
+      <c r="B360">
+        <f t="shared" si="5"/>
+        <v>0.50649283347247054</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A361">
+        <v>0.36</v>
+      </c>
+      <c r="B361">
+        <f t="shared" si="5"/>
+        <v>0.50742898259327385</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A362">
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="B362">
+        <f t="shared" si="5"/>
+        <v>0.50836432194309888</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A363">
+        <v>0.36199999999999999</v>
+      </c>
+      <c r="B363">
+        <f t="shared" si="5"/>
+        <v>0.50929885440768563</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A364">
+        <v>0.36299999999999999</v>
+      </c>
+      <c r="B364">
+        <f t="shared" si="5"/>
+        <v>0.51023258285474438</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A365">
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="B365">
+        <f t="shared" si="5"/>
+        <v>0.51116551013411737</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A366">
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="B366">
+        <f t="shared" si="5"/>
+        <v>0.51209763907793648</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A367">
+        <v>0.36599999999999999</v>
+      </c>
+      <c r="B367">
+        <f t="shared" si="5"/>
+        <v>0.51302897250078128</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A368">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="B368">
+        <f t="shared" si="5"/>
+        <v>0.51395951319983413</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A369">
+        <v>0.36799999999999999</v>
+      </c>
+      <c r="B369">
+        <f t="shared" si="5"/>
+        <v>0.51488926395503309</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A370">
+        <v>0.36899999999999999</v>
+      </c>
+      <c r="B370">
+        <f t="shared" si="5"/>
+        <v>0.51581822752922424</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A371">
+        <v>0.37</v>
+      </c>
+      <c r="B371">
+        <f t="shared" si="5"/>
+        <v>0.51674640666831173</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A372">
+        <v>0.371</v>
+      </c>
+      <c r="B372">
+        <f t="shared" si="5"/>
+        <v>0.51767380410140551</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A373">
+        <v>0.372</v>
+      </c>
+      <c r="B373">
+        <f t="shared" si="5"/>
+        <v>0.51860042254096861</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A374">
+        <v>0.373</v>
+      </c>
+      <c r="B374">
+        <f t="shared" si="5"/>
+        <v>0.51952626468296148</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A375">
+        <v>0.374</v>
+      </c>
+      <c r="B375">
+        <f t="shared" si="5"/>
+        <v>0.52045133320698567</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A376">
+        <v>0.375</v>
+      </c>
+      <c r="B376">
+        <f t="shared" si="5"/>
+        <v>0.52137563077642557</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A377">
+        <v>0.376</v>
+      </c>
+      <c r="B377">
+        <f t="shared" si="5"/>
+        <v>0.52229916003858812</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A378">
+        <v>0.377</v>
+      </c>
+      <c r="B378">
+        <f t="shared" si="5"/>
+        <v>0.52322192362484177</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A379">
+        <v>0.378</v>
+      </c>
+      <c r="B379">
+        <f t="shared" si="5"/>
+        <v>0.52414392415075317</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A380">
+        <v>0.379</v>
+      </c>
+      <c r="B380">
+        <f t="shared" si="5"/>
+        <v>0.52506516421622296</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A381">
+        <v>0.38</v>
+      </c>
+      <c r="B381">
+        <f t="shared" si="5"/>
+        <v>0.52598564640561929</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A382">
+        <v>0.38100000000000001</v>
+      </c>
+      <c r="B382">
+        <f t="shared" si="5"/>
+        <v>0.52690537328791043</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A383">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="B383">
+        <f t="shared" si="5"/>
+        <v>0.52782434741679607</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A384">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="B384">
+        <f t="shared" si="5"/>
+        <v>0.52874257133083613</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A385">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="B385">
+        <f t="shared" si="5"/>
+        <v>0.52966004755357998</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A386">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="B386">
+        <f t="shared" si="5"/>
+        <v>0.53057677859369201</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A387">
+        <v>0.38600000000000001</v>
+      </c>
+      <c r="B387">
+        <f t="shared" ref="B387:B450" si="6">EXP(LN(A387 + 0.009076778736745) / 1.46927)</f>
+        <v>0.53149276694507797</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A388">
+        <v>0.38700000000000001</v>
+      </c>
+      <c r="B388">
+        <f t="shared" si="6"/>
+        <v>0.53240801508700775</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A389">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="B389">
+        <f t="shared" si="6"/>
+        <v>0.53332252548423942</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A390">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="B390">
+        <f t="shared" si="6"/>
+        <v>0.53423630058713911</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A391">
+        <v>0.39</v>
+      </c>
+      <c r="B391">
+        <f t="shared" si="6"/>
+        <v>0.53514934283180193</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A392">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="B392">
+        <f t="shared" si="6"/>
+        <v>0.53606165464017053</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A393">
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="B393">
+        <f t="shared" si="6"/>
+        <v>0.53697323842015166</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A394">
+        <v>0.39300000000000002</v>
+      </c>
+      <c r="B394">
+        <f t="shared" si="6"/>
+        <v>0.53788409656573333</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A395">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="B395">
+        <f t="shared" si="6"/>
+        <v>0.53879423145709904</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A396">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="B396">
+        <f t="shared" si="6"/>
+        <v>0.53970364546074145</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A397">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="B397">
+        <f t="shared" si="6"/>
+        <v>0.54061234092957511</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A398">
+        <v>0.39700000000000002</v>
+      </c>
+      <c r="B398">
+        <f t="shared" si="6"/>
+        <v>0.54152032020304774</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A399">
+        <v>0.39800000000000002</v>
+      </c>
+      <c r="B399">
+        <f t="shared" si="6"/>
+        <v>0.54242758560724968</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A400">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="B400">
+        <f t="shared" si="6"/>
+        <v>0.54333413945502329</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A401">
+        <v>0.4</v>
+      </c>
+      <c r="B401">
+        <f t="shared" si="6"/>
+        <v>0.54423998404607032</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A402">
+        <v>0.40100000000000002</v>
+      </c>
+      <c r="B402">
+        <f t="shared" si="6"/>
+        <v>0.54514512166705908</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A403">
+        <v>0.40200000000000002</v>
+      </c>
+      <c r="B403">
+        <f t="shared" si="6"/>
+        <v>0.5460495545917291</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A404">
+        <v>0.40300000000000002</v>
+      </c>
+      <c r="B404">
+        <f t="shared" si="6"/>
+        <v>0.54695328508099617</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A405">
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="B405">
+        <f t="shared" si="6"/>
+        <v>0.54785631538305513</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A406">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="B406">
+        <f t="shared" si="6"/>
+        <v>0.54875864773348249</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A407">
+        <v>0.40600000000000003</v>
+      </c>
+      <c r="B407">
+        <f t="shared" si="6"/>
+        <v>0.54966028435533698</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A408">
+        <v>0.40699999999999997</v>
+      </c>
+      <c r="B408">
+        <f t="shared" si="6"/>
+        <v>0.55056122745926017</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A409">
+        <v>0.40799999999999997</v>
+      </c>
+      <c r="B409">
+        <f t="shared" si="6"/>
+        <v>0.55146147924357514</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A410">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="B410">
+        <f t="shared" si="6"/>
+        <v>0.55236104189438484</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A411">
+        <v>0.41</v>
+      </c>
+      <c r="B411">
+        <f t="shared" si="6"/>
+        <v>0.55325991758566861</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A412">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="B412">
+        <f t="shared" si="6"/>
+        <v>0.55415810847937841</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A413">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="B413">
+        <f t="shared" si="6"/>
+        <v>0.55505561672553383</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A414">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="B414">
+        <f t="shared" si="6"/>
+        <v>0.55595244446231629</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A415">
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="B415">
+        <f t="shared" si="6"/>
+        <v>0.5568485938161617</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A416">
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="B416">
+        <f t="shared" si="6"/>
+        <v>0.55774406690185285</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A417">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="B417">
+        <f t="shared" si="6"/>
+        <v>0.55863886582261058</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A418">
+        <v>0.41699999999999998</v>
+      </c>
+      <c r="B418">
+        <f t="shared" si="6"/>
+        <v>0.55953299267018386</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A419">
+        <v>0.41799999999999998</v>
+      </c>
+      <c r="B419">
+        <f t="shared" si="6"/>
+        <v>0.5604264495249397</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A420">
+        <v>0.41899999999999998</v>
+      </c>
+      <c r="B420">
+        <f t="shared" si="6"/>
+        <v>0.56131923845595044</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A421">
+        <v>0.42</v>
+      </c>
+      <c r="B421">
+        <f t="shared" si="6"/>
+        <v>0.56221136152108264</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A422">
+        <v>0.42099999999999999</v>
+      </c>
+      <c r="B422">
+        <f t="shared" si="6"/>
+        <v>0.56310282076708285</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A423">
+        <v>0.42199999999999999</v>
+      </c>
+      <c r="B423">
+        <f t="shared" si="6"/>
+        <v>0.56399361822966343</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A424">
+        <v>0.42299999999999999</v>
+      </c>
+      <c r="B424">
+        <f t="shared" si="6"/>
+        <v>0.56488375593358808</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A425">
+        <v>0.42399999999999999</v>
+      </c>
+      <c r="B425">
+        <f t="shared" si="6"/>
+        <v>0.5657732358927553</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A426">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="B426">
+        <f t="shared" si="6"/>
+        <v>0.56666206011028197</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A427">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="B427">
+        <f t="shared" si="6"/>
+        <v>0.56755023057858578</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A428">
+        <v>0.42699999999999999</v>
+      </c>
+      <c r="B428">
+        <f t="shared" si="6"/>
+        <v>0.56843774927946666</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A429">
+        <v>0.42799999999999999</v>
+      </c>
+      <c r="B429">
+        <f t="shared" si="6"/>
+        <v>0.56932461818418745</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A430">
+        <v>0.42899999999999999</v>
+      </c>
+      <c r="B430">
+        <f t="shared" si="6"/>
+        <v>0.57021083925355454</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A431">
+        <v>0.43</v>
+      </c>
+      <c r="B431">
+        <f t="shared" si="6"/>
+        <v>0.57109641443799597</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A432">
+        <v>0.43099999999999999</v>
+      </c>
+      <c r="B432">
+        <f t="shared" si="6"/>
+        <v>0.57198134567764114</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A433">
+        <v>0.432</v>
+      </c>
+      <c r="B433">
+        <f t="shared" si="6"/>
+        <v>0.57286563490239761</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A434">
+        <v>0.433</v>
+      </c>
+      <c r="B434">
+        <f t="shared" si="6"/>
+        <v>0.57374928403202807</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A435">
+        <v>0.434</v>
+      </c>
+      <c r="B435">
+        <f t="shared" si="6"/>
+        <v>0.57463229497622681</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A436">
+        <v>0.435</v>
+      </c>
+      <c r="B436">
+        <f t="shared" si="6"/>
+        <v>0.575514669634695</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A437">
+        <v>0.436</v>
+      </c>
+      <c r="B437">
+        <f t="shared" si="6"/>
+        <v>0.57639640989721508</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A438">
+        <v>0.437</v>
+      </c>
+      <c r="B438">
+        <f t="shared" si="6"/>
+        <v>0.57727751764372515</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A439">
+        <v>0.438</v>
+      </c>
+      <c r="B439">
+        <f t="shared" si="6"/>
+        <v>0.57815799474439189</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A440">
+        <v>0.439</v>
+      </c>
+      <c r="B440">
+        <f t="shared" si="6"/>
+        <v>0.5790378430596832</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A441">
+        <v>0.44</v>
+      </c>
+      <c r="B441">
+        <f t="shared" si="6"/>
+        <v>0.57991706444044022</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A442">
+        <v>0.441</v>
+      </c>
+      <c r="B442">
+        <f t="shared" si="6"/>
+        <v>0.58079566072794775</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A443">
+        <v>0.442</v>
+      </c>
+      <c r="B443">
+        <f t="shared" si="6"/>
+        <v>0.58167363375400571</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A444">
+        <v>0.443</v>
+      </c>
+      <c r="B444">
+        <f t="shared" si="6"/>
+        <v>0.58255098534099814</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A445">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="B445">
+        <f t="shared" si="6"/>
+        <v>0.58342771730196274</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A446">
+        <v>0.44500000000000001</v>
+      </c>
+      <c r="B446">
+        <f t="shared" si="6"/>
+        <v>0.58430383144065878</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A447">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="B447">
+        <f t="shared" si="6"/>
+        <v>0.58517932955163598</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A448">
+        <v>0.44700000000000001</v>
+      </c>
+      <c r="B448">
+        <f t="shared" si="6"/>
+        <v>0.58605421342030017</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A449">
+        <v>0.44800000000000001</v>
+      </c>
+      <c r="B449">
+        <f t="shared" si="6"/>
+        <v>0.58692848482298121</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A450">
+        <v>0.44900000000000001</v>
+      </c>
+      <c r="B450">
+        <f t="shared" si="6"/>
+        <v>0.58780214552699794</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A451">
+        <v>0.45</v>
+      </c>
+      <c r="B451">
+        <f t="shared" ref="B451:B514" si="7">EXP(LN(A451 + 0.009076778736745) / 1.46927)</f>
+        <v>0.58867519729072393</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A452">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="B452">
+        <f t="shared" si="7"/>
+        <v>0.58954764186365205</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A453">
+        <v>0.45200000000000001</v>
+      </c>
+      <c r="B453">
+        <f t="shared" si="7"/>
+        <v>0.59041948098645858</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A454">
+        <v>0.45300000000000001</v>
+      </c>
+      <c r="B454">
+        <f t="shared" si="7"/>
+        <v>0.59129071639106601</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A455">
+        <v>0.45400000000000001</v>
+      </c>
+      <c r="B455">
+        <f t="shared" si="7"/>
+        <v>0.59216134980070712</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A456">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="B456">
+        <f t="shared" si="7"/>
+        <v>0.59303138292998614</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A457">
+        <v>0.45600000000000002</v>
+      </c>
+      <c r="B457">
+        <f t="shared" si="7"/>
+        <v>0.59390081748494106</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A458">
+        <v>0.45700000000000002</v>
+      </c>
+      <c r="B458">
+        <f t="shared" si="7"/>
+        <v>0.59476965516310465</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A459">
+        <v>0.45800000000000002</v>
+      </c>
+      <c r="B459">
+        <f t="shared" si="7"/>
+        <v>0.59563789765356456</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A460">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="B460">
+        <f t="shared" si="7"/>
+        <v>0.59650554663702415</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A461">
+        <v>0.46</v>
+      </c>
+      <c r="B461">
+        <f t="shared" si="7"/>
+        <v>0.59737260378586132</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A462">
+        <v>0.46100000000000002</v>
+      </c>
+      <c r="B462">
+        <f t="shared" si="7"/>
+        <v>0.59823907076418725</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A463">
+        <v>0.46200000000000002</v>
+      </c>
+      <c r="B463">
+        <f t="shared" si="7"/>
+        <v>0.59910494922790547</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A464">
+        <v>0.46300000000000002</v>
+      </c>
+      <c r="B464">
+        <f t="shared" si="7"/>
+        <v>0.59997024082476902</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A465">
+        <v>0.46400000000000002</v>
+      </c>
+      <c r="B465">
+        <f t="shared" si="7"/>
+        <v>0.6008349471944382</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A466">
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="B466">
+        <f t="shared" si="7"/>
+        <v>0.60169906996853684</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A467">
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="B467">
+        <f t="shared" si="7"/>
+        <v>0.60256261077070894</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A468">
+        <v>0.46700000000000003</v>
+      </c>
+      <c r="B468">
+        <f t="shared" si="7"/>
+        <v>0.60342557121667439</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A469">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="B469">
+        <f t="shared" si="7"/>
+        <v>0.60428795291428405</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A470">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="B470">
+        <f t="shared" si="7"/>
+        <v>0.60514975746357447</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A471">
+        <v>0.47</v>
+      </c>
+      <c r="B471">
+        <f t="shared" si="7"/>
+        <v>0.60601098645682216</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A472">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="B472">
+        <f t="shared" si="7"/>
+        <v>0.60687164147859773</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A473">
+        <v>0.47199999999999998</v>
+      </c>
+      <c r="B473">
+        <f t="shared" si="7"/>
+        <v>0.60773172410581844</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A474">
+        <v>0.47299999999999998</v>
+      </c>
+      <c r="B474">
+        <f t="shared" si="7"/>
+        <v>0.60859123590780129</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A475">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="B475">
+        <f t="shared" si="7"/>
+        <v>0.60945017844631566</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A476">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="B476">
+        <f t="shared" si="7"/>
+        <v>0.61030855327563482</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A477">
+        <v>0.47599999999999998</v>
+      </c>
+      <c r="B477">
+        <f t="shared" si="7"/>
+        <v>0.61116636194258733</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A478">
+        <v>0.47699999999999998</v>
+      </c>
+      <c r="B478">
+        <f t="shared" si="7"/>
+        <v>0.6120236059866081</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A479">
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="B479">
+        <f t="shared" si="7"/>
+        <v>0.61288028693978858</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A480">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="B480">
+        <f t="shared" si="7"/>
+        <v>0.61373640632692728</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A481">
+        <v>0.48</v>
+      </c>
+      <c r="B481">
+        <f t="shared" si="7"/>
+        <v>0.61459196566557894</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A482">
+        <v>0.48099999999999998</v>
+      </c>
+      <c r="B482">
+        <f t="shared" si="7"/>
+        <v>0.61544696646610375</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A483">
+        <v>0.48199999999999998</v>
+      </c>
+      <c r="B483">
+        <f t="shared" si="7"/>
+        <v>0.61630141023171614</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A484">
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="B484">
+        <f t="shared" si="7"/>
+        <v>0.61715529845853323</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A485">
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="B485">
+        <f t="shared" si="7"/>
+        <v>0.61800863263562222</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A486">
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="B486">
+        <f t="shared" si="7"/>
+        <v>0.61886141424504837</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A487">
+        <v>0.48599999999999999</v>
+      </c>
+      <c r="B487">
+        <f t="shared" si="7"/>
+        <v>0.61971364476192159</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A488">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="B488">
+        <f t="shared" si="7"/>
+        <v>0.62056532565444344</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A489">
+        <v>0.48799999999999999</v>
+      </c>
+      <c r="B489">
+        <f t="shared" si="7"/>
+        <v>0.6214164583839531</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A490">
+        <v>0.48899999999999999</v>
+      </c>
+      <c r="B490">
+        <f t="shared" si="7"/>
+        <v>0.62226704440497294</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A491">
+        <v>0.49</v>
+      </c>
+      <c r="B491">
+        <f t="shared" si="7"/>
+        <v>0.62311708516525477</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A492">
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="B492">
+        <f t="shared" si="7"/>
+        <v>0.62396658210582367</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A493">
+        <v>0.49199999999999999</v>
+      </c>
+      <c r="B493">
+        <f t="shared" si="7"/>
+        <v>0.62481553666102396</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A494">
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="B494">
+        <f t="shared" si="7"/>
+        <v>0.62566395025856214</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A495">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="B495">
+        <f t="shared" si="7"/>
+        <v>0.62651182431955177</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A496">
+        <v>0.495</v>
+      </c>
+      <c r="B496">
+        <f t="shared" si="7"/>
+        <v>0.62735916025855643</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A497">
+        <v>0.496</v>
+      </c>
+      <c r="B497">
+        <f t="shared" si="7"/>
+        <v>0.628205959483633</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A498">
+        <v>0.497</v>
+      </c>
+      <c r="B498">
+        <f t="shared" si="7"/>
+        <v>0.62905222339637412</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A499">
+        <v>0.498</v>
+      </c>
+      <c r="B499">
+        <f t="shared" si="7"/>
+        <v>0.62989795339195143</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A500">
+        <v>0.499</v>
+      </c>
+      <c r="B500">
+        <f t="shared" si="7"/>
+        <v>0.63074315085915622</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A501">
+        <v>0.5</v>
+      </c>
+      <c r="B501">
+        <f t="shared" si="7"/>
+        <v>0.63158781718044266</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A502">
+        <v>0.501</v>
+      </c>
+      <c r="B502">
+        <f t="shared" si="7"/>
+        <v>0.6324319537319677</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A503">
+        <v>0.502</v>
+      </c>
+      <c r="B503">
+        <f t="shared" si="7"/>
+        <v>0.6332755618836331</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A504">
+        <v>0.503</v>
+      </c>
+      <c r="B504">
+        <f t="shared" si="7"/>
+        <v>0.63411864299912524</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A505">
+        <v>0.504</v>
+      </c>
+      <c r="B505">
+        <f t="shared" si="7"/>
+        <v>0.634961198435956</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A506">
+        <v>0.505</v>
+      </c>
+      <c r="B506">
+        <f t="shared" si="7"/>
+        <v>0.63580322954550239</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A507">
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="B507">
+        <f t="shared" si="7"/>
+        <v>0.6366447376730463</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A508">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="B508">
+        <f t="shared" si="7"/>
+        <v>0.63748572415781346</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A509">
+        <v>0.50800000000000001</v>
+      </c>
+      <c r="B509">
+        <f t="shared" si="7"/>
+        <v>0.63832619033301286</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A510">
+        <v>0.50900000000000001</v>
+      </c>
+      <c r="B510">
+        <f t="shared" si="7"/>
+        <v>0.63916613752587503</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A511">
+        <v>0.51</v>
+      </c>
+      <c r="B511">
+        <f t="shared" si="7"/>
+        <v>0.64000556705769029</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A512">
+        <v>0.51100000000000001</v>
+      </c>
+      <c r="B512">
+        <f t="shared" si="7"/>
+        <v>0.64084448024384699</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A513">
+        <v>0.51200000000000001</v>
+      </c>
+      <c r="B513">
+        <f t="shared" si="7"/>
+        <v>0.64168287839386895</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A514">
+        <v>0.51300000000000001</v>
+      </c>
+      <c r="B514">
+        <f t="shared" si="7"/>
+        <v>0.64252076281145287</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A515">
+        <v>0.51400000000000001</v>
+      </c>
+      <c r="B515">
+        <f t="shared" ref="B515:B578" si="8">EXP(LN(A515 + 0.009076778736745) / 1.46927)</f>
+        <v>0.64335813479450554</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A516">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="B516">
+        <f t="shared" si="8"/>
+        <v>0.64419499563518012</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A517">
+        <v>0.51600000000000001</v>
+      </c>
+      <c r="B517">
+        <f t="shared" si="8"/>
+        <v>0.64503134661991313</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A518">
+        <v>0.51700000000000002</v>
+      </c>
+      <c r="B518">
+        <f t="shared" si="8"/>
+        <v>0.64586718902946016</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A519">
+        <v>0.51800000000000002</v>
+      </c>
+      <c r="B519">
+        <f t="shared" si="8"/>
+        <v>0.64670252413893192</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A520">
+        <v>0.51900000000000002</v>
+      </c>
+      <c r="B520">
+        <f t="shared" si="8"/>
+        <v>0.64753735321782979</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A521">
+        <v>0.52</v>
+      </c>
+      <c r="B521">
+        <f t="shared" si="8"/>
+        <v>0.64837167753008063</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A522">
+        <v>0.52100000000000002</v>
+      </c>
+      <c r="B522">
+        <f t="shared" si="8"/>
+        <v>0.64920549833407259</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A523">
+        <v>0.52200000000000002</v>
+      </c>
+      <c r="B523">
+        <f t="shared" si="8"/>
+        <v>0.65003881688268905</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A524">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="B524">
+        <f t="shared" si="8"/>
+        <v>0.65087163442334328</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A525">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="B525">
+        <f t="shared" si="8"/>
+        <v>0.65170395219801247</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A526">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="B526">
+        <f t="shared" si="8"/>
+        <v>0.65253577144327191</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A527">
+        <v>0.52600000000000002</v>
+      </c>
+      <c r="B527">
+        <f t="shared" si="8"/>
+        <v>0.65336709339032784</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A528">
+        <v>0.52700000000000002</v>
+      </c>
+      <c r="B528">
+        <f t="shared" si="8"/>
+        <v>0.65419791926505166</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A529">
+        <v>0.52800000000000002</v>
+      </c>
+      <c r="B529">
+        <f t="shared" si="8"/>
+        <v>0.65502825028801215</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A530">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="B530">
+        <f t="shared" si="8"/>
+        <v>0.65585808767450882</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A531">
+        <v>0.53</v>
+      </c>
+      <c r="B531">
+        <f t="shared" si="8"/>
+        <v>0.65668743263460383</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A532">
+        <v>0.53100000000000003</v>
+      </c>
+      <c r="B532">
+        <f t="shared" si="8"/>
+        <v>0.65751628637315507</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A533">
+        <v>0.53200000000000003</v>
+      </c>
+      <c r="B533">
+        <f t="shared" si="8"/>
+        <v>0.65834465008984699</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A534">
+        <v>0.53300000000000003</v>
+      </c>
+      <c r="B534">
+        <f t="shared" si="8"/>
+        <v>0.6591725249792233</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A535">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="B535">
+        <f t="shared" si="8"/>
+        <v>0.65999991223071841</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A536">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="B536">
+        <f t="shared" si="8"/>
+        <v>0.66082681302868751</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A537">
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="B537">
+        <f t="shared" si="8"/>
+        <v>0.66165322855243924</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A538">
+        <v>0.53700000000000003</v>
+      </c>
+      <c r="B538">
+        <f t="shared" si="8"/>
+        <v>0.66247915997626505</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A539">
+        <v>0.53800000000000003</v>
+      </c>
+      <c r="B539">
+        <f t="shared" si="8"/>
+        <v>0.66330460846947037</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A540">
+        <v>0.53900000000000003</v>
+      </c>
+      <c r="B540">
+        <f t="shared" si="8"/>
+        <v>0.66412957519640448</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A541">
+        <v>0.54</v>
+      </c>
+      <c r="B541">
+        <f t="shared" si="8"/>
+        <v>0.66495406131649104</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A542">
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="B542">
+        <f t="shared" si="8"/>
+        <v>0.66577806798425732</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A543">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="B543">
+        <f t="shared" si="8"/>
+        <v>0.66660159634936389</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A544">
+        <v>0.54300000000000004</v>
+      </c>
+      <c r="B544">
+        <f t="shared" si="8"/>
+        <v>0.66742464755663422</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A545">
+        <v>0.54400000000000004</v>
+      </c>
+      <c r="B545">
+        <f t="shared" si="8"/>
+        <v>0.66824722274608317</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A546">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="B546">
+        <f t="shared" si="8"/>
+        <v>0.66906932305294664</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A547">
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="B547">
+        <f t="shared" si="8"/>
+        <v>0.66989094960770934</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A548">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="B548">
+        <f t="shared" si="8"/>
+        <v>0.67071210353613375</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A549">
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="B549">
+        <f t="shared" si="8"/>
+        <v>0.67153278595928845</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A550">
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="B550">
+        <f t="shared" si="8"/>
+        <v>0.67235299799357506</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A551">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="B551">
+        <f t="shared" si="8"/>
+        <v>0.67317274075075739</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A552">
+        <v>0.55100000000000005</v>
+      </c>
+      <c r="B552">
+        <f t="shared" si="8"/>
+        <v>0.67399201533798803</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A553">
+        <v>0.55200000000000005</v>
+      </c>
+      <c r="B553">
+        <f t="shared" si="8"/>
+        <v>0.67481082285783589</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A554">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="B554">
+        <f t="shared" si="8"/>
+        <v>0.67562916440831355</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A555">
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="B555">
+        <f t="shared" si="8"/>
+        <v>0.67644704108290354</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A556">
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="B556">
+        <f t="shared" si="8"/>
+        <v>0.67726445397058588</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A557">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="B557">
+        <f t="shared" si="8"/>
+        <v>0.67808140415586393</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A558">
+        <v>0.55700000000000005</v>
+      </c>
+      <c r="B558">
+        <f t="shared" si="8"/>
+        <v>0.67889789271879109</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A559">
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="B559">
+        <f t="shared" si="8"/>
+        <v>0.67971392073499648</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A560">
+        <v>0.55900000000000005</v>
+      </c>
+      <c r="B560">
+        <f t="shared" si="8"/>
+        <v>0.68052948927571111</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A561">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="B561">
+        <f t="shared" si="8"/>
+        <v>0.68134459940779357</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A562">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="B562">
+        <f t="shared" si="8"/>
+        <v>0.68215925219375539</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A563">
+        <v>0.56200000000000006</v>
+      </c>
+      <c r="B563">
+        <f t="shared" si="8"/>
+        <v>0.68297344869178633</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A564">
+        <v>0.56299999999999994</v>
+      </c>
+      <c r="B564">
+        <f t="shared" si="8"/>
+        <v>0.6837871899557797</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A565">
+        <v>0.56399999999999995</v>
+      </c>
+      <c r="B565">
+        <f t="shared" si="8"/>
+        <v>0.68460047703535731</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A566">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="B566">
+        <f t="shared" si="8"/>
+        <v>0.68541331097589375</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A567">
+        <v>0.56599999999999995</v>
+      </c>
+      <c r="B567">
+        <f t="shared" si="8"/>
+        <v>0.6862256928185414</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A568">
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="B568">
+        <f t="shared" si="8"/>
+        <v>0.68703762360025478</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A569">
+        <v>0.56799999999999995</v>
+      </c>
+      <c r="B569">
+        <f t="shared" si="8"/>
+        <v>0.6878491043538143</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A570">
+        <v>0.56899999999999995</v>
+      </c>
+      <c r="B570">
+        <f t="shared" si="8"/>
+        <v>0.68866013610785071</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A571">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="B571">
+        <f t="shared" si="8"/>
+        <v>0.68947071988686859</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A572">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="B572">
+        <f t="shared" si="8"/>
+        <v>0.69028085671127071</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A573">
+        <v>0.57199999999999995</v>
+      </c>
+      <c r="B573">
+        <f t="shared" si="8"/>
+        <v>0.69109054759738042</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A574">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="B574">
+        <f t="shared" si="8"/>
+        <v>0.69189979355746556</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A575">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="B575">
+        <f t="shared" si="8"/>
+        <v>0.69270859559976161</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A576">
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="B576">
+        <f t="shared" si="8"/>
+        <v>0.69351695472849473</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A577">
+        <v>0.57599999999999996</v>
+      </c>
+      <c r="B577">
+        <f t="shared" si="8"/>
+        <v>0.69432487194390391</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A578">
+        <v>0.57699999999999996</v>
+      </c>
+      <c r="B578">
+        <f t="shared" si="8"/>
+        <v>0.69513234824226444</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A579">
+        <v>0.57799999999999996</v>
+      </c>
+      <c r="B579">
+        <f t="shared" ref="B579:B642" si="9">EXP(LN(A579 + 0.009076778736745) / 1.46927)</f>
+        <v>0.69593938461590976</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A580">
+        <v>0.57899999999999996</v>
+      </c>
+      <c r="B580">
+        <f t="shared" si="9"/>
+        <v>0.69674598205325367</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A581">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="B581">
+        <f t="shared" si="9"/>
+        <v>0.69755214153881306</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A582">
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="B582">
+        <f t="shared" si="9"/>
+        <v>0.69835786405322953</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A583">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="B583">
+        <f t="shared" si="9"/>
+        <v>0.69916315057329081</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A584">
+        <v>0.58299999999999996</v>
+      </c>
+      <c r="B584">
+        <f t="shared" si="9"/>
+        <v>0.69996800207195298</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A585">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="B585">
+        <f t="shared" si="9"/>
+        <v>0.70077241951836156</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A586">
+        <v>0.58499999999999996</v>
+      </c>
+      <c r="B586">
+        <f t="shared" si="9"/>
+        <v>0.70157640387787312</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A587">
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="B587">
+        <f t="shared" si="9"/>
+        <v>0.70237995611207626</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A588">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="B588">
+        <f t="shared" si="9"/>
+        <v>0.70318307717881257</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A589">
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="B589">
+        <f t="shared" si="9"/>
+        <v>0.7039857680321977</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A590">
+        <v>0.58899999999999997</v>
+      </c>
+      <c r="B590">
+        <f t="shared" si="9"/>
+        <v>0.70478802962264187</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A591">
+        <v>0.59</v>
+      </c>
+      <c r="B591">
+        <f t="shared" si="9"/>
+        <v>0.70558986289687053</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A592">
+        <v>0.59099999999999997</v>
+      </c>
+      <c r="B592">
+        <f t="shared" si="9"/>
+        <v>0.70639126879794489</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A593">
+        <v>0.59199999999999997</v>
+      </c>
+      <c r="B593">
+        <f t="shared" si="9"/>
+        <v>0.70719224826528182</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A594">
+        <v>0.59299999999999997</v>
+      </c>
+      <c r="B594">
+        <f t="shared" si="9"/>
+        <v>0.70799280223467431</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A595">
+        <v>0.59399999999999997</v>
+      </c>
+      <c r="B595">
+        <f t="shared" si="9"/>
+        <v>0.70879293163831147</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A596">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="B596">
+        <f t="shared" si="9"/>
+        <v>0.70959263740479783</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A597">
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="B597">
+        <f t="shared" si="9"/>
+        <v>0.71039192045917376</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A598">
+        <v>0.59699999999999998</v>
+      </c>
+      <c r="B598">
+        <f t="shared" si="9"/>
+        <v>0.7111907817229346</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A599">
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="B599">
+        <f t="shared" si="9"/>
+        <v>0.71198922211405025</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A600">
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="B600">
+        <f t="shared" si="9"/>
+        <v>0.71278724254698411</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A601">
+        <v>0.6</v>
+      </c>
+      <c r="B601">
+        <f t="shared" si="9"/>
+        <v>0.7135848439327126</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A602">
+        <v>0.60099999999999998</v>
+      </c>
+      <c r="B602">
+        <f t="shared" si="9"/>
+        <v>0.71438202717874399</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A603">
+        <v>0.60199999999999998</v>
+      </c>
+      <c r="B603">
+        <f t="shared" si="9"/>
+        <v>0.71517879318913724</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A604">
+        <v>0.60299999999999998</v>
+      </c>
+      <c r="B604">
+        <f t="shared" si="9"/>
+        <v>0.71597514286452091</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A605">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="B605">
+        <f t="shared" si="9"/>
+        <v>0.71677107710211152</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A606">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="B606">
+        <f t="shared" si="9"/>
+        <v>0.71756659679573198</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A607">
+        <v>0.60599999999999998</v>
+      </c>
+      <c r="B607">
+        <f t="shared" si="9"/>
+        <v>0.71836170283583045</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A608">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="B608">
+        <f t="shared" si="9"/>
+        <v>0.71915639610949778</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A609">
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="B609">
+        <f t="shared" si="9"/>
+        <v>0.71995067750048625</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A610">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="B610">
+        <f t="shared" si="9"/>
+        <v>0.72074454788922693</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A611">
+        <v>0.61</v>
+      </c>
+      <c r="B611">
+        <f t="shared" si="9"/>
+        <v>0.72153800815284841</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A612">
+        <v>0.61099999999999999</v>
+      </c>
+      <c r="B612">
+        <f t="shared" si="9"/>
+        <v>0.72233105916519336</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A613">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="B613">
+        <f t="shared" si="9"/>
+        <v>0.72312370179683705</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A614">
+        <v>0.61299999999999999</v>
+      </c>
+      <c r="B614">
+        <f t="shared" si="9"/>
+        <v>0.72391593691510436</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A615">
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="B615">
+        <f t="shared" si="9"/>
+        <v>0.72470776538408688</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A616">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="B616">
+        <f t="shared" si="9"/>
+        <v>0.72549918806466107</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A617">
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="B617">
+        <f t="shared" si="9"/>
+        <v>0.72629020581450432</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A618">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="B618">
+        <f t="shared" si="9"/>
+        <v>0.72708081948811243</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A619">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="B619">
+        <f t="shared" si="9"/>
+        <v>0.7278710299368164</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A620">
+        <v>0.61899999999999999</v>
+      </c>
+      <c r="B620">
+        <f t="shared" si="9"/>
+        <v>0.72866083800879933</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A621">
+        <v>0.62</v>
+      </c>
+      <c r="B621">
+        <f t="shared" si="9"/>
+        <v>0.72945024454911278</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A622">
+        <v>0.621</v>
+      </c>
+      <c r="B622">
+        <f t="shared" si="9"/>
+        <v>0.7302392503996934</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A623">
+        <v>0.622</v>
+      </c>
+      <c r="B623">
+        <f t="shared" si="9"/>
+        <v>0.73102785639937917</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A624">
+        <v>0.623</v>
+      </c>
+      <c r="B624">
+        <f t="shared" si="9"/>
+        <v>0.73181606338392646</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A625">
+        <v>0.624</v>
+      </c>
+      <c r="B625">
+        <f t="shared" si="9"/>
+        <v>0.73260387218602496</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A626">
+        <v>0.625</v>
+      </c>
+      <c r="B626">
+        <f t="shared" si="9"/>
+        <v>0.73339128363531481</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A627">
+        <v>0.626</v>
+      </c>
+      <c r="B627">
+        <f t="shared" si="9"/>
+        <v>0.734178298558402</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A628">
+        <v>0.627</v>
+      </c>
+      <c r="B628">
+        <f t="shared" si="9"/>
+        <v>0.73496491777887452</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A629">
+        <v>0.628</v>
+      </c>
+      <c r="B629">
+        <f t="shared" si="9"/>
+        <v>0.73575114211731785</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A630">
+        <v>0.629</v>
+      </c>
+      <c r="B630">
+        <f t="shared" si="9"/>
+        <v>0.73653697239133087</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A631">
+        <v>0.63</v>
+      </c>
+      <c r="B631">
+        <f t="shared" si="9"/>
+        <v>0.73732240941554117</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A632">
+        <v>0.63100000000000001</v>
+      </c>
+      <c r="B632">
+        <f t="shared" si="9"/>
+        <v>0.73810745400162048</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A633">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="B633">
+        <f t="shared" si="9"/>
+        <v>0.73889210695830021</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A634">
+        <v>0.63300000000000001</v>
+      </c>
+      <c r="B634">
+        <f t="shared" si="9"/>
+        <v>0.73967636909138657</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A635">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="B635">
+        <f t="shared" si="9"/>
+        <v>0.74046024120377552</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A636">
+        <v>0.63500000000000001</v>
+      </c>
+      <c r="B636">
+        <f t="shared" si="9"/>
+        <v>0.74124372409546802</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A637">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="B637">
+        <f t="shared" si="9"/>
+        <v>0.74202681856358466</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A638">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="B638">
+        <f t="shared" si="9"/>
+        <v>0.74280952540238099</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A639">
+        <v>0.63800000000000001</v>
+      </c>
+      <c r="B639">
+        <f t="shared" si="9"/>
+        <v>0.74359184540326173</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A640">
+        <v>0.63900000000000001</v>
+      </c>
+      <c r="B640">
+        <f t="shared" si="9"/>
+        <v>0.74437377935479554</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A641">
+        <v>0.64</v>
+      </c>
+      <c r="B641">
+        <f t="shared" si="9"/>
+        <v>0.74515532804272966</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A642">
+        <v>0.64100000000000001</v>
+      </c>
+      <c r="B642">
+        <f t="shared" si="9"/>
+        <v>0.74593649225000425</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A643">
+        <v>0.64200000000000002</v>
+      </c>
+      <c r="B643">
+        <f t="shared" ref="B643:B706" si="10">EXP(LN(A643 + 0.009076778736745) / 1.46927)</f>
+        <v>0.74671727275676669</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A644">
+        <v>0.64300000000000002</v>
+      </c>
+      <c r="B644">
+        <f t="shared" si="10"/>
+        <v>0.74749767034038583</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A645">
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="B645">
+        <f t="shared" si="10"/>
+        <v>0.74827768577546616</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A646">
+        <v>0.64500000000000002</v>
+      </c>
+      <c r="B646">
+        <f t="shared" si="10"/>
+        <v>0.74905731983386203</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A647">
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="B647">
+        <f t="shared" si="10"/>
+        <v>0.74983657328469111</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A648">
+        <v>0.64700000000000002</v>
+      </c>
+      <c r="B648">
+        <f t="shared" si="10"/>
+        <v>0.75061544689434867</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A649">
+        <v>0.64800000000000002</v>
+      </c>
+      <c r="B649">
+        <f t="shared" si="10"/>
+        <v>0.75139394142652138</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A650">
+        <v>0.64900000000000002</v>
+      </c>
+      <c r="B650">
+        <f t="shared" si="10"/>
+        <v>0.75217205764220074</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A651">
+        <v>0.65</v>
+      </c>
+      <c r="B651">
+        <f t="shared" si="10"/>
+        <v>0.75294979629969683</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A652">
+        <v>0.65100000000000002</v>
+      </c>
+      <c r="B652">
+        <f t="shared" si="10"/>
+        <v>0.75372715815465174</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A653">
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="B653">
+        <f t="shared" si="10"/>
+        <v>0.75450414396005283</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A654">
+        <v>0.65300000000000002</v>
+      </c>
+      <c r="B654">
+        <f t="shared" si="10"/>
+        <v>0.75528075446624665</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A655">
+        <v>0.65400000000000003</v>
+      </c>
+      <c r="B655">
+        <f t="shared" si="10"/>
+        <v>0.75605699042095154</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A656">
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="B656">
+        <f t="shared" si="10"/>
+        <v>0.75683285256927069</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A657">
+        <v>0.65600000000000003</v>
+      </c>
+      <c r="B657">
+        <f t="shared" si="10"/>
+        <v>0.75760834165370616</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A658">
+        <v>0.65700000000000003</v>
+      </c>
+      <c r="B658">
+        <f t="shared" si="10"/>
+        <v>0.75838345841417087</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A659">
+        <v>0.65800000000000003</v>
+      </c>
+      <c r="B659">
+        <f t="shared" si="10"/>
+        <v>0.75915820358800168</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A660">
+        <v>0.65900000000000003</v>
+      </c>
+      <c r="B660">
+        <f t="shared" si="10"/>
+        <v>0.75993257790997271</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A661">
+        <v>0.66</v>
+      </c>
+      <c r="B661">
+        <f t="shared" si="10"/>
+        <v>0.76070658211230768</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A662">
+        <v>0.66100000000000003</v>
+      </c>
+      <c r="B662">
+        <f t="shared" si="10"/>
+        <v>0.76148021692469248</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A663">
+        <v>0.66200000000000003</v>
+      </c>
+      <c r="B663">
+        <f t="shared" si="10"/>
+        <v>0.76225348307428797</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A664">
+        <v>0.66300000000000003</v>
+      </c>
+      <c r="B664">
+        <f t="shared" si="10"/>
+        <v>0.76302638128574241</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A665">
+        <v>0.66400000000000003</v>
+      </c>
+      <c r="B665">
+        <f t="shared" si="10"/>
+        <v>0.76379891228120367</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A666">
+        <v>0.66500000000000004</v>
+      </c>
+      <c r="B666">
+        <f t="shared" si="10"/>
+        <v>0.76457107678033198</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A667">
+        <v>0.66600000000000004</v>
+      </c>
+      <c r="B667">
+        <f t="shared" si="10"/>
+        <v>0.76534287550031166</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A668">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="B668">
+        <f t="shared" si="10"/>
+        <v>0.76611430915586376</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A669">
+        <v>0.66800000000000004</v>
+      </c>
+      <c r="B669">
+        <f t="shared" si="10"/>
+        <v>0.76688537845925775</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A670">
+        <v>0.66900000000000004</v>
+      </c>
+      <c r="B670">
+        <f t="shared" si="10"/>
+        <v>0.76765608412032393</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A671">
+        <v>0.67</v>
+      </c>
+      <c r="B671">
+        <f t="shared" si="10"/>
+        <v>0.768426426846465</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A672">
+        <v>0.67100000000000004</v>
+      </c>
+      <c r="B672">
+        <f t="shared" si="10"/>
+        <v>0.76919640734266825</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A673">
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="B673">
+        <f t="shared" si="10"/>
+        <v>0.76996602631151689</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A674">
+        <v>0.67300000000000004</v>
+      </c>
+      <c r="B674">
+        <f t="shared" si="10"/>
+        <v>0.7707352844532025</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A675">
+        <v>0.67400000000000004</v>
+      </c>
+      <c r="B675">
+        <f t="shared" si="10"/>
+        <v>0.77150418246553565</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A676">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="B676">
+        <f t="shared" si="10"/>
+        <v>0.77227272104395872</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A677">
+        <v>0.67600000000000005</v>
+      </c>
+      <c r="B677">
+        <f t="shared" si="10"/>
+        <v>0.77304090088155608</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A678">
+        <v>0.67700000000000005</v>
+      </c>
+      <c r="B678">
+        <f t="shared" si="10"/>
+        <v>0.77380872266906664</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A679">
+        <v>0.67800000000000005</v>
+      </c>
+      <c r="B679">
+        <f t="shared" si="10"/>
+        <v>0.7745761870948944</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A680">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="B680">
+        <f t="shared" si="10"/>
+        <v>0.77534329484512021</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A681">
+        <v>0.68</v>
+      </c>
+      <c r="B681">
+        <f t="shared" si="10"/>
+        <v>0.77611004660351246</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A682">
+        <v>0.68100000000000005</v>
+      </c>
+      <c r="B682">
+        <f t="shared" si="10"/>
+        <v>0.77687644305153902</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A683">
+        <v>0.68200000000000005</v>
+      </c>
+      <c r="B683">
+        <f t="shared" si="10"/>
+        <v>0.7776424848683775</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A684">
+        <v>0.68300000000000005</v>
+      </c>
+      <c r="B684">
+        <f t="shared" si="10"/>
+        <v>0.77840817273092677</v>
+      </c>
+    </row>
+    <row r="685" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A685">
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="B685">
+        <f t="shared" si="10"/>
+        <v>0.77917350731381751</v>
+      </c>
+    </row>
+    <row r="686" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A686">
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="B686">
+        <f t="shared" si="10"/>
+        <v>0.77993848928942333</v>
+      </c>
+    </row>
+    <row r="687" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A687">
+        <v>0.68600000000000005</v>
+      </c>
+      <c r="B687">
+        <f t="shared" si="10"/>
+        <v>0.78070311932787162</v>
+      </c>
+    </row>
+    <row r="688" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A688">
+        <v>0.68700000000000006</v>
+      </c>
+      <c r="B688">
+        <f t="shared" si="10"/>
+        <v>0.78146739809705401</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A689">
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="B689">
+        <f t="shared" si="10"/>
+        <v>0.78223132626263703</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A690">
+        <v>0.68899999999999995</v>
+      </c>
+      <c r="B690">
+        <f t="shared" si="10"/>
+        <v>0.7829949044880733</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A691">
+        <v>0.69</v>
+      </c>
+      <c r="B691">
+        <f t="shared" si="10"/>
+        <v>0.7837581334346112</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A692">
+        <v>0.69099999999999995</v>
+      </c>
+      <c r="B692">
+        <f t="shared" si="10"/>
+        <v>0.78452101376130567</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A693">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="B693">
+        <f t="shared" si="10"/>
+        <v>0.78528354612502904</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A694">
+        <v>0.69299999999999995</v>
+      </c>
+      <c r="B694">
+        <f t="shared" si="10"/>
+        <v>0.7860457311804806</v>
+      </c>
+    </row>
+    <row r="695" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A695">
+        <v>0.69399999999999995</v>
+      </c>
+      <c r="B695">
+        <f t="shared" si="10"/>
+        <v>0.78680756958019737</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A696">
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="B696">
+        <f t="shared" si="10"/>
+        <v>0.78756906197456444</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A697">
+        <v>0.69599999999999995</v>
+      </c>
+      <c r="B697">
+        <f t="shared" si="10"/>
+        <v>0.78833020901182449</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A698">
+        <v>0.69699999999999995</v>
+      </c>
+      <c r="B698">
+        <f t="shared" si="10"/>
+        <v>0.78909101133808845</v>
+      </c>
+    </row>
+    <row r="699" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A699">
+        <v>0.69799999999999995</v>
+      </c>
+      <c r="B699">
+        <f t="shared" si="10"/>
+        <v>0.78985146959734531</v>
+      </c>
+    </row>
+    <row r="700" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A700">
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="B700">
+        <f t="shared" si="10"/>
+        <v>0.79061158443147217</v>
+      </c>
+    </row>
+    <row r="701" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A701">
+        <v>0.7</v>
+      </c>
+      <c r="B701">
+        <f t="shared" si="10"/>
+        <v>0.79137135648024393</v>
+      </c>
+    </row>
+    <row r="702" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A702">
+        <v>0.70099999999999996</v>
+      </c>
+      <c r="B702">
+        <f t="shared" si="10"/>
+        <v>0.79213078638134315</v>
+      </c>
+    </row>
+    <row r="703" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A703">
+        <v>0.70199999999999996</v>
+      </c>
+      <c r="B703">
+        <f t="shared" si="10"/>
+        <v>0.79288987477037021</v>
+      </c>
+    </row>
+    <row r="704" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A704">
+        <v>0.70299999999999996</v>
+      </c>
+      <c r="B704">
+        <f t="shared" si="10"/>
+        <v>0.79364862228085264</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A705">
+        <v>0.70399999999999996</v>
+      </c>
+      <c r="B705">
+        <f t="shared" si="10"/>
+        <v>0.79440702954425468</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A706">
+        <v>0.70499999999999996</v>
+      </c>
+      <c r="B706">
+        <f t="shared" si="10"/>
+        <v>0.79516509718998751</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A707">
+        <v>0.70599999999999996</v>
+      </c>
+      <c r="B707">
+        <f t="shared" ref="B707:B770" si="11">EXP(LN(A707 + 0.009076778736745) / 1.46927)</f>
+        <v>0.79592282584541796</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A708">
+        <v>0.70699999999999996</v>
+      </c>
+      <c r="B708">
+        <f t="shared" si="11"/>
+        <v>0.7966802161358788</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A709">
+        <v>0.70799999999999996</v>
+      </c>
+      <c r="B709">
+        <f t="shared" si="11"/>
+        <v>0.79743726868467735</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A710">
+        <v>0.70899999999999996</v>
+      </c>
+      <c r="B710">
+        <f t="shared" si="11"/>
+        <v>0.79819398411310571</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A711">
+        <v>0.71</v>
+      </c>
+      <c r="B711">
+        <f t="shared" si="11"/>
+        <v>0.79895036304044942</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A712">
+        <v>0.71099999999999997</v>
+      </c>
+      <c r="B712">
+        <f t="shared" si="11"/>
+        <v>0.79970640608399701</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A713">
+        <v>0.71199999999999997</v>
+      </c>
+      <c r="B713">
+        <f t="shared" si="11"/>
+        <v>0.80046211385904908</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A714">
+        <v>0.71299999999999997</v>
+      </c>
+      <c r="B714">
+        <f t="shared" si="11"/>
+        <v>0.80121748697892747</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A715">
+        <v>0.71399999999999997</v>
+      </c>
+      <c r="B715">
+        <f t="shared" si="11"/>
+        <v>0.8019725260549847</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A716">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="B716">
+        <f t="shared" si="11"/>
+        <v>0.8027272316966122</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A717">
+        <v>0.71599999999999997</v>
+      </c>
+      <c r="B717">
+        <f t="shared" si="11"/>
+        <v>0.80348160451125039</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A718">
+        <v>0.71699999999999997</v>
+      </c>
+      <c r="B718">
+        <f t="shared" si="11"/>
+        <v>0.8042356451043966</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A719">
+        <v>0.71799999999999997</v>
+      </c>
+      <c r="B719">
+        <f t="shared" si="11"/>
+        <v>0.80498935407961447</v>
+      </c>
+    </row>
+    <row r="720" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A720">
+        <v>0.71899999999999997</v>
+      </c>
+      <c r="B720">
+        <f t="shared" si="11"/>
+        <v>0.80574273203854274</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A721">
+        <v>0.72</v>
+      </c>
+      <c r="B721">
+        <f t="shared" si="11"/>
+        <v>0.8064957795809039</v>
+      </c>
+    </row>
+    <row r="722" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A722">
+        <v>0.72099999999999997</v>
+      </c>
+      <c r="B722">
+        <f t="shared" si="11"/>
+        <v>0.80724849730451309</v>
+      </c>
+    </row>
+    <row r="723" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A723">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="B723">
+        <f t="shared" si="11"/>
+        <v>0.80800088580528651</v>
+      </c>
+    </row>
+    <row r="724" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A724">
+        <v>0.72299999999999998</v>
+      </c>
+      <c r="B724">
+        <f t="shared" si="11"/>
+        <v>0.8087529456772502</v>
+      </c>
+    </row>
+    <row r="725" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A725">
+        <v>0.72399999999999998</v>
+      </c>
+      <c r="B725">
+        <f t="shared" si="11"/>
+        <v>0.80950467751254884</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A726">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="B726">
+        <f t="shared" si="11"/>
+        <v>0.81025608190145371</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A727">
+        <v>0.72599999999999998</v>
+      </c>
+      <c r="B727">
+        <f t="shared" si="11"/>
+        <v>0.81100715943237167</v>
+      </c>
+    </row>
+    <row r="728" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A728">
+        <v>0.72699999999999998</v>
+      </c>
+      <c r="B728">
+        <f t="shared" si="11"/>
+        <v>0.81175791069185321</v>
+      </c>
+    </row>
+    <row r="729" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A729">
+        <v>0.72799999999999998</v>
+      </c>
+      <c r="B729">
+        <f t="shared" si="11"/>
+        <v>0.81250833626460117</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A730">
+        <v>0.72899999999999998</v>
+      </c>
+      <c r="B730">
+        <f t="shared" si="11"/>
+        <v>0.81325843673347864</v>
+      </c>
+    </row>
+    <row r="731" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A731">
+        <v>0.73</v>
+      </c>
+      <c r="B731">
+        <f t="shared" si="11"/>
+        <v>0.81400821267951795</v>
+      </c>
+    </row>
+    <row r="732" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A732">
+        <v>0.73099999999999998</v>
+      </c>
+      <c r="B732">
+        <f t="shared" si="11"/>
+        <v>0.81475766468192778</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A733">
+        <v>0.73199999999999998</v>
+      </c>
+      <c r="B733">
+        <f t="shared" si="11"/>
+        <v>0.81550679331810239</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A734">
+        <v>0.73299999999999998</v>
+      </c>
+      <c r="B734">
+        <f t="shared" si="11"/>
+        <v>0.81625559916362922</v>
+      </c>
+    </row>
+    <row r="735" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A735">
+        <v>0.73399999999999999</v>
+      </c>
+      <c r="B735">
+        <f t="shared" si="11"/>
+        <v>0.81700408279229697</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A736">
+        <v>0.73499999999999999</v>
+      </c>
+      <c r="B736">
+        <f t="shared" si="11"/>
+        <v>0.81775224477610398</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A737">
+        <v>0.73599999999999999</v>
+      </c>
+      <c r="B737">
+        <f t="shared" si="11"/>
+        <v>0.81850008568526578</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A738">
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="B738">
+        <f t="shared" si="11"/>
+        <v>0.81924760608822322</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A739">
+        <v>0.73799999999999999</v>
+      </c>
+      <c r="B739">
+        <f t="shared" si="11"/>
+        <v>0.81999480655165047</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A740">
+        <v>0.73899999999999999</v>
+      </c>
+      <c r="B740">
+        <f t="shared" si="11"/>
+        <v>0.82074168764046274</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A741">
+        <v>0.74</v>
+      </c>
+      <c r="B741">
+        <f t="shared" si="11"/>
+        <v>0.82148824991782399</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A742">
+        <v>0.74099999999999999</v>
+      </c>
+      <c r="B742">
+        <f t="shared" si="11"/>
+        <v>0.82223449394515502</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A743">
+        <v>0.74199999999999999</v>
+      </c>
+      <c r="B743">
+        <f t="shared" si="11"/>
+        <v>0.82298042028214069</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A744">
+        <v>0.74299999999999999</v>
+      </c>
+      <c r="B744">
+        <f t="shared" si="11"/>
+        <v>0.82372602948673823</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A745">
+        <v>0.74399999999999999</v>
+      </c>
+      <c r="B745">
+        <f t="shared" si="11"/>
+        <v>0.82447132211518404</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A746">
+        <v>0.745</v>
+      </c>
+      <c r="B746">
+        <f t="shared" si="11"/>
+        <v>0.82521629872200231</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A747">
+        <v>0.746</v>
+      </c>
+      <c r="B747">
+        <f t="shared" si="11"/>
+        <v>0.82596095986001161</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A748">
+        <v>0.747</v>
+      </c>
+      <c r="B748">
+        <f t="shared" si="11"/>
+        <v>0.82670530608033266</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A749">
+        <v>0.748</v>
+      </c>
+      <c r="B749">
+        <f t="shared" si="11"/>
+        <v>0.82744933793239617</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A750">
+        <v>0.749</v>
+      </c>
+      <c r="B750">
+        <f t="shared" si="11"/>
+        <v>0.82819305596394988</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A751">
+        <v>0.75</v>
+      </c>
+      <c r="B751">
+        <f t="shared" si="11"/>
+        <v>0.82893646072106586</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A752">
+        <v>0.751</v>
+      </c>
+      <c r="B752">
+        <f t="shared" si="11"/>
+        <v>0.8296795527481482</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A753">
+        <v>0.752</v>
+      </c>
+      <c r="B753">
+        <f t="shared" si="11"/>
+        <v>0.83042233258793996</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A754">
+        <v>0.753</v>
+      </c>
+      <c r="B754">
+        <f t="shared" si="11"/>
+        <v>0.83116480078153043</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A755">
+        <v>0.754</v>
+      </c>
+      <c r="B755">
+        <f t="shared" si="11"/>
+        <v>0.83190695786836277</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A756">
+        <v>0.755</v>
+      </c>
+      <c r="B756">
+        <f t="shared" si="11"/>
+        <v>0.83264880438624034</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A757">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="B757">
+        <f t="shared" si="11"/>
+        <v>0.83339034087133479</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A758">
+        <v>0.75700000000000001</v>
+      </c>
+      <c r="B758">
+        <f t="shared" si="11"/>
+        <v>0.83413156785819242</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A759">
+        <v>0.75800000000000001</v>
+      </c>
+      <c r="B759">
+        <f t="shared" si="11"/>
+        <v>0.83487248587974128</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A760">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="B760">
+        <f t="shared" si="11"/>
+        <v>0.83561309546729889</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A761">
+        <v>0.76</v>
+      </c>
+      <c r="B761">
+        <f t="shared" si="11"/>
+        <v>0.8363533971505781</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A762">
+        <v>0.76100000000000001</v>
+      </c>
+      <c r="B762">
+        <f t="shared" si="11"/>
+        <v>0.83709339145769501</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A763">
+        <v>0.76200000000000001</v>
+      </c>
+      <c r="B763">
+        <f t="shared" si="11"/>
+        <v>0.837833078915175</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A764">
+        <v>0.76300000000000001</v>
+      </c>
+      <c r="B764">
+        <f t="shared" si="11"/>
+        <v>0.83857246004796038</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A765">
+        <v>0.76400000000000001</v>
+      </c>
+      <c r="B765">
+        <f t="shared" si="11"/>
+        <v>0.83931153537941672</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A766">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="B766">
+        <f t="shared" si="11"/>
+        <v>0.84005030543133941</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A767">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="B767">
+        <f t="shared" si="11"/>
+        <v>0.84078877072396108</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A768">
+        <v>0.76700000000000002</v>
+      </c>
+      <c r="B768">
+        <f t="shared" si="11"/>
+        <v>0.84152693177595772</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A769">
+        <v>0.76800000000000002</v>
+      </c>
+      <c r="B769">
+        <f t="shared" si="11"/>
+        <v>0.84226478910445546</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A770">
+        <v>0.76900000000000002</v>
+      </c>
+      <c r="B770">
+        <f t="shared" si="11"/>
+        <v>0.84300234322503742</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A771">
+        <v>0.77</v>
+      </c>
+      <c r="B771">
+        <f t="shared" ref="B771:B834" si="12">EXP(LN(A771 + 0.009076778736745) / 1.46927)</f>
+        <v>0.84373959465174997</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A772">
+        <v>0.77100000000000002</v>
+      </c>
+      <c r="B772">
+        <f t="shared" si="12"/>
+        <v>0.84447654389710958</v>
+      </c>
+    </row>
+    <row r="773" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A773">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="B773">
+        <f t="shared" si="12"/>
+        <v>0.84521319147210894</v>
+      </c>
+    </row>
+    <row r="774" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A774">
+        <v>0.77300000000000002</v>
+      </c>
+      <c r="B774">
+        <f t="shared" si="12"/>
+        <v>0.84594953788622385</v>
+      </c>
+    </row>
+    <row r="775" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A775">
+        <v>0.77400000000000002</v>
+      </c>
+      <c r="B775">
+        <f t="shared" si="12"/>
+        <v>0.84668558364741953</v>
+      </c>
+    </row>
+    <row r="776" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A776">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="B776">
+        <f t="shared" si="12"/>
+        <v>0.84742132926215663</v>
+      </c>
+    </row>
+    <row r="777" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A777">
+        <v>0.77600000000000002</v>
+      </c>
+      <c r="B777">
+        <f t="shared" si="12"/>
+        <v>0.84815677523539834</v>
+      </c>
+    </row>
+    <row r="778" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A778">
+        <v>0.77700000000000002</v>
+      </c>
+      <c r="B778">
+        <f t="shared" si="12"/>
+        <v>0.84889192207061615</v>
+      </c>
+    </row>
+    <row r="779" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A779">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="B779">
+        <f t="shared" si="12"/>
+        <v>0.84962677026979616</v>
+      </c>
+    </row>
+    <row r="780" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A780">
+        <v>0.77900000000000003</v>
+      </c>
+      <c r="B780">
+        <f t="shared" si="12"/>
+        <v>0.8503613203334458</v>
+      </c>
+    </row>
+    <row r="781" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A781">
+        <v>0.78</v>
+      </c>
+      <c r="B781">
+        <f t="shared" si="12"/>
+        <v>0.85109557276059955</v>
+      </c>
+    </row>
+    <row r="782" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A782">
+        <v>0.78100000000000003</v>
+      </c>
+      <c r="B782">
+        <f t="shared" si="12"/>
+        <v>0.85182952804882528</v>
+      </c>
+    </row>
+    <row r="783" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A783">
+        <v>0.78200000000000003</v>
+      </c>
+      <c r="B783">
+        <f t="shared" si="12"/>
+        <v>0.8525631866942307</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A784">
+        <v>0.78300000000000003</v>
+      </c>
+      <c r="B784">
+        <f t="shared" si="12"/>
+        <v>0.85329654919146913</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A785">
+        <v>0.78400000000000003</v>
+      </c>
+      <c r="B785">
+        <f t="shared" si="12"/>
+        <v>0.85402961603374561</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A786">
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="B786">
+        <f t="shared" si="12"/>
+        <v>0.8547623877128232</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A787">
+        <v>0.78600000000000003</v>
+      </c>
+      <c r="B787">
+        <f t="shared" si="12"/>
+        <v>0.85549486471902891</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A788">
+        <v>0.78700000000000003</v>
+      </c>
+      <c r="B788">
+        <f t="shared" si="12"/>
+        <v>0.85622704754125967</v>
+      </c>
+    </row>
+    <row r="789" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A789">
+        <v>0.78800000000000003</v>
+      </c>
+      <c r="B789">
+        <f t="shared" si="12"/>
+        <v>0.85695893666698797</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A790">
+        <v>0.78900000000000003</v>
+      </c>
+      <c r="B790">
+        <f t="shared" si="12"/>
+        <v>0.85769053258226835</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A791">
+        <v>0.79</v>
+      </c>
+      <c r="B791">
+        <f t="shared" si="12"/>
+        <v>0.85842183577174336</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A792">
+        <v>0.79100000000000004</v>
+      </c>
+      <c r="B792">
+        <f t="shared" si="12"/>
+        <v>0.85915284671864844</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A793">
+        <v>0.79200000000000004</v>
+      </c>
+      <c r="B793">
+        <f t="shared" si="12"/>
+        <v>0.85988356590481896</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A794">
+        <v>0.79300000000000004</v>
+      </c>
+      <c r="B794">
+        <f t="shared" si="12"/>
+        <v>0.86061399381069525</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A795">
+        <v>0.79400000000000004</v>
+      </c>
+      <c r="B795">
+        <f t="shared" si="12"/>
+        <v>0.86134413091532869</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A796">
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="B796">
+        <f t="shared" si="12"/>
+        <v>0.86207397769638727</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A797">
+        <v>0.79600000000000004</v>
+      </c>
+      <c r="B797">
+        <f t="shared" si="12"/>
+        <v>0.86280353463016157</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A798">
+        <v>0.79700000000000004</v>
+      </c>
+      <c r="B798">
+        <f t="shared" si="12"/>
+        <v>0.86353280219157025</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A799">
+        <v>0.79800000000000004</v>
+      </c>
+      <c r="B799">
+        <f t="shared" si="12"/>
+        <v>0.8642617808541655</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A800">
+        <v>0.79900000000000004</v>
+      </c>
+      <c r="B800">
+        <f t="shared" si="12"/>
+        <v>0.86499047109013905</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A801">
+        <v>0.8</v>
+      </c>
+      <c r="B801">
+        <f t="shared" si="12"/>
+        <v>0.8657188733703276</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A802">
+        <v>0.80100000000000005</v>
+      </c>
+      <c r="B802">
+        <f t="shared" si="12"/>
+        <v>0.86644698816421828</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A803">
+        <v>0.80200000000000005</v>
+      </c>
+      <c r="B803">
+        <f t="shared" si="12"/>
+        <v>0.86717481593995449</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A804">
+        <v>0.80300000000000005</v>
+      </c>
+      <c r="B804">
+        <f t="shared" si="12"/>
+        <v>0.86790235716434072</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A805">
+        <v>0.80400000000000005</v>
+      </c>
+      <c r="B805">
+        <f t="shared" si="12"/>
+        <v>0.86862961230284885</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A806">
+        <v>0.80500000000000005</v>
+      </c>
+      <c r="B806">
+        <f t="shared" si="12"/>
+        <v>0.86935658181962305</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A807">
+        <v>0.80600000000000005</v>
+      </c>
+      <c r="B807">
+        <f t="shared" si="12"/>
+        <v>0.87008326617748544</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A808">
+        <v>0.80700000000000005</v>
+      </c>
+      <c r="B808">
+        <f t="shared" si="12"/>
+        <v>0.87080966583794139</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A809">
+        <v>0.80800000000000005</v>
+      </c>
+      <c r="B809">
+        <f t="shared" si="12"/>
+        <v>0.87153578126118481</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A810">
+        <v>0.80900000000000005</v>
+      </c>
+      <c r="B810">
+        <f t="shared" si="12"/>
+        <v>0.87226161290610349</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A811">
+        <v>0.81</v>
+      </c>
+      <c r="B811">
+        <f t="shared" si="12"/>
+        <v>0.87298716123028441</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A812">
+        <v>0.81100000000000005</v>
+      </c>
+      <c r="B812">
+        <f t="shared" si="12"/>
+        <v>0.87371242669001936</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A813">
+        <v>0.81200000000000006</v>
+      </c>
+      <c r="B813">
+        <f t="shared" si="12"/>
+        <v>0.87443740974030959</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A814">
+        <v>0.81299999999999994</v>
+      </c>
+      <c r="B814">
+        <f t="shared" si="12"/>
+        <v>0.87516211083487128</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A815">
+        <v>0.81399999999999995</v>
+      </c>
+      <c r="B815">
+        <f t="shared" si="12"/>
+        <v>0.87588653042614095</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A816">
+        <v>0.81499999999999995</v>
+      </c>
+      <c r="B816">
+        <f t="shared" si="12"/>
+        <v>0.87661066896528028</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A817">
+        <v>0.81599999999999995</v>
+      </c>
+      <c r="B817">
+        <f t="shared" si="12"/>
+        <v>0.87733452690218139</v>
+      </c>
+    </row>
+    <row r="818" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A818">
+        <v>0.81699999999999995</v>
+      </c>
+      <c r="B818">
+        <f t="shared" si="12"/>
+        <v>0.87805810468547196</v>
+      </c>
+    </row>
+    <row r="819" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A819">
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="B819">
+        <f t="shared" si="12"/>
+        <v>0.87878140276252048</v>
+      </c>
+    </row>
+    <row r="820" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A820">
+        <v>0.81899999999999995</v>
+      </c>
+      <c r="B820">
+        <f t="shared" si="12"/>
+        <v>0.87950442157944064</v>
+      </c>
+    </row>
+    <row r="821" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A821">
+        <v>0.82</v>
+      </c>
+      <c r="B821">
+        <f t="shared" si="12"/>
+        <v>0.88022716158109737</v>
+      </c>
+    </row>
+    <row r="822" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A822">
+        <v>0.82099999999999995</v>
+      </c>
+      <c r="B822">
+        <f t="shared" si="12"/>
+        <v>0.88094962321111103</v>
+      </c>
+    </row>
+    <row r="823" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A823">
+        <v>0.82199999999999995</v>
+      </c>
+      <c r="B823">
+        <f t="shared" si="12"/>
+        <v>0.88167180691186264</v>
+      </c>
+    </row>
+    <row r="824" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A824">
+        <v>0.82299999999999995</v>
+      </c>
+      <c r="B824">
+        <f t="shared" si="12"/>
+        <v>0.88239371312449888</v>
+      </c>
+    </row>
+    <row r="825" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A825">
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="B825">
+        <f t="shared" si="12"/>
+        <v>0.88311534228893718</v>
+      </c>
+    </row>
+    <row r="826" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A826">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="B826">
+        <f t="shared" si="12"/>
+        <v>0.88383669484387006</v>
+      </c>
+    </row>
+    <row r="827" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A827">
+        <v>0.82599999999999996</v>
+      </c>
+      <c r="B827">
+        <f t="shared" si="12"/>
+        <v>0.88455777122677071</v>
+      </c>
+    </row>
+    <row r="828" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A828">
+        <v>0.82699999999999996</v>
+      </c>
+      <c r="B828">
+        <f t="shared" si="12"/>
+        <v>0.88527857187389714</v>
+      </c>
+    </row>
+    <row r="829" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A829">
+        <v>0.82799999999999996</v>
+      </c>
+      <c r="B829">
+        <f t="shared" si="12"/>
+        <v>0.88599909722029768</v>
+      </c>
+    </row>
+    <row r="830" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A830">
+        <v>0.82899999999999996</v>
+      </c>
+      <c r="B830">
+        <f t="shared" si="12"/>
+        <v>0.88671934769981531</v>
+      </c>
+    </row>
+    <row r="831" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A831">
+        <v>0.83</v>
+      </c>
+      <c r="B831">
+        <f t="shared" si="12"/>
+        <v>0.8874393237450926</v>
+      </c>
+    </row>
+    <row r="832" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A832">
+        <v>0.83099999999999996</v>
+      </c>
+      <c r="B832">
+        <f t="shared" si="12"/>
+        <v>0.88815902578757622</v>
+      </c>
+    </row>
+    <row r="833" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A833">
+        <v>0.83199999999999996</v>
+      </c>
+      <c r="B833">
+        <f t="shared" si="12"/>
+        <v>0.88887845425752221</v>
+      </c>
+    </row>
+    <row r="834" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A834">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="B834">
+        <f t="shared" si="12"/>
+        <v>0.88959760958400014</v>
+      </c>
+    </row>
+    <row r="835" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A835">
+        <v>0.83399999999999996</v>
+      </c>
+      <c r="B835">
+        <f t="shared" ref="B835:B898" si="13">EXP(LN(A835 + 0.009076778736745) / 1.46927)</f>
+        <v>0.89031649219489806</v>
+      </c>
+    </row>
+    <row r="836" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A836">
+        <v>0.83499999999999996</v>
+      </c>
+      <c r="B836">
+        <f t="shared" si="13"/>
+        <v>0.89103510251692697</v>
+      </c>
+    </row>
+    <row r="837" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A837">
+        <v>0.83599999999999997</v>
+      </c>
+      <c r="B837">
+        <f t="shared" si="13"/>
+        <v>0.8917534409756257</v>
+      </c>
+    </row>
+    <row r="838" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A838">
+        <v>0.83699999999999997</v>
+      </c>
+      <c r="B838">
+        <f t="shared" si="13"/>
+        <v>0.89247150799536534</v>
+      </c>
+    </row>
+    <row r="839" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A839">
+        <v>0.83799999999999997</v>
+      </c>
+      <c r="B839">
+        <f t="shared" si="13"/>
+        <v>0.89318930399935381</v>
+      </c>
+    </row>
+    <row r="840" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A840">
+        <v>0.83899999999999997</v>
+      </c>
+      <c r="B840">
+        <f t="shared" si="13"/>
+        <v>0.89390682940964039</v>
+      </c>
+    </row>
+    <row r="841" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A841">
+        <v>0.84</v>
+      </c>
+      <c r="B841">
+        <f t="shared" si="13"/>
+        <v>0.8946240846471204</v>
+      </c>
+    </row>
+    <row r="842" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A842">
+        <v>0.84099999999999997</v>
+      </c>
+      <c r="B842">
+        <f t="shared" si="13"/>
+        <v>0.89534107013153974</v>
+      </c>
+    </row>
+    <row r="843" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A843">
+        <v>0.84199999999999997</v>
+      </c>
+      <c r="B843">
+        <f t="shared" si="13"/>
+        <v>0.89605778628149901</v>
+      </c>
+    </row>
+    <row r="844" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A844">
+        <v>0.84299999999999997</v>
+      </c>
+      <c r="B844">
+        <f t="shared" si="13"/>
+        <v>0.89677423351445851</v>
+      </c>
+    </row>
+    <row r="845" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A845">
+        <v>0.84399999999999997</v>
+      </c>
+      <c r="B845">
+        <f t="shared" si="13"/>
+        <v>0.8974904122467422</v>
+      </c>
+    </row>
+    <row r="846" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A846">
+        <v>0.84499999999999997</v>
+      </c>
+      <c r="B846">
+        <f t="shared" si="13"/>
+        <v>0.89820632289354241</v>
+      </c>
+    </row>
+    <row r="847" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A847">
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="B847">
+        <f t="shared" si="13"/>
+        <v>0.89892196586892426</v>
+      </c>
+    </row>
+    <row r="848" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A848">
+        <v>0.84699999999999998</v>
+      </c>
+      <c r="B848">
+        <f t="shared" si="13"/>
+        <v>0.89963734158582964</v>
+      </c>
+    </row>
+    <row r="849" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A849">
+        <v>0.84799999999999998</v>
+      </c>
+      <c r="B849">
+        <f t="shared" si="13"/>
+        <v>0.90035245045608225</v>
+      </c>
+    </row>
+    <row r="850" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A850">
+        <v>0.84899999999999998</v>
+      </c>
+      <c r="B850">
+        <f t="shared" si="13"/>
+        <v>0.90106729289039111</v>
+      </c>
+    </row>
+    <row r="851" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A851">
+        <v>0.85</v>
+      </c>
+      <c r="B851">
+        <f t="shared" si="13"/>
+        <v>0.90178186929835569</v>
+      </c>
+    </row>
+    <row r="852" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A852">
+        <v>0.85099999999999998</v>
+      </c>
+      <c r="B852">
+        <f t="shared" si="13"/>
+        <v>0.90249618008846955</v>
+      </c>
+    </row>
+    <row r="853" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A853">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="B853">
+        <f t="shared" si="13"/>
+        <v>0.90321022566812492</v>
+      </c>
+    </row>
+    <row r="854" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A854">
+        <v>0.85299999999999998</v>
+      </c>
+      <c r="B854">
+        <f t="shared" si="13"/>
+        <v>0.90392400644361681</v>
+      </c>
+    </row>
+    <row r="855" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A855">
+        <v>0.85399999999999998</v>
+      </c>
+      <c r="B855">
+        <f t="shared" si="13"/>
+        <v>0.90463752282014753</v>
+      </c>
+    </row>
+    <row r="856" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A856">
+        <v>0.85499999999999998</v>
+      </c>
+      <c r="B856">
+        <f t="shared" si="13"/>
+        <v>0.90535077520183049</v>
+      </c>
+    </row>
+    <row r="857" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A857">
+        <v>0.85599999999999998</v>
+      </c>
+      <c r="B857">
+        <f t="shared" si="13"/>
+        <v>0.90606376399169464</v>
+      </c>
+    </row>
+    <row r="858" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A858">
+        <v>0.85699999999999998</v>
+      </c>
+      <c r="B858">
+        <f t="shared" si="13"/>
+        <v>0.90677648959168844</v>
+      </c>
+    </row>
+    <row r="859" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A859">
+        <v>0.85799999999999998</v>
+      </c>
+      <c r="B859">
+        <f t="shared" si="13"/>
+        <v>0.90748895240268423</v>
+      </c>
+    </row>
+    <row r="860" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A860">
+        <v>0.85899999999999999</v>
+      </c>
+      <c r="B860">
+        <f t="shared" si="13"/>
+        <v>0.90820115282448211</v>
+      </c>
+    </row>
+    <row r="861" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A861">
+        <v>0.86</v>
+      </c>
+      <c r="B861">
+        <f t="shared" si="13"/>
+        <v>0.90891309125581443</v>
+      </c>
+    </row>
+    <row r="862" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A862">
+        <v>0.86099999999999999</v>
+      </c>
+      <c r="B862">
+        <f t="shared" si="13"/>
+        <v>0.90962476809434922</v>
+      </c>
+    </row>
+    <row r="863" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A863">
+        <v>0.86199999999999999</v>
+      </c>
+      <c r="B863">
+        <f t="shared" si="13"/>
+        <v>0.910336183736695</v>
+      </c>
+    </row>
+    <row r="864" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A864">
+        <v>0.86299999999999999</v>
+      </c>
+      <c r="B864">
+        <f t="shared" si="13"/>
+        <v>0.91104733857840403</v>
+      </c>
+    </row>
+    <row r="865" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A865">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="B865">
+        <f t="shared" si="13"/>
+        <v>0.91175823301397718</v>
+      </c>
+    </row>
+    <row r="866" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A866">
+        <v>0.86499999999999999</v>
+      </c>
+      <c r="B866">
+        <f t="shared" si="13"/>
+        <v>0.91246886743686728</v>
+      </c>
+    </row>
+    <row r="867" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A867">
+        <v>0.86599999999999999</v>
+      </c>
+      <c r="B867">
+        <f t="shared" si="13"/>
+        <v>0.91317924223948321</v>
+      </c>
+    </row>
+    <row r="868" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A868">
+        <v>0.86699999999999999</v>
+      </c>
+      <c r="B868">
+        <f t="shared" si="13"/>
+        <v>0.91388935781319414</v>
+      </c>
+    </row>
+    <row r="869" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A869">
+        <v>0.86799999999999999</v>
+      </c>
+      <c r="B869">
+        <f t="shared" si="13"/>
+        <v>0.91459921454833326</v>
+      </c>
+    </row>
+    <row r="870" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A870">
+        <v>0.86899999999999999</v>
+      </c>
+      <c r="B870">
+        <f t="shared" si="13"/>
+        <v>0.91530881283420162</v>
+      </c>
+    </row>
+    <row r="871" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A871">
+        <v>0.87</v>
+      </c>
+      <c r="B871">
+        <f t="shared" si="13"/>
+        <v>0.91601815305907219</v>
+      </c>
+    </row>
+    <row r="872" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A872">
+        <v>0.871</v>
+      </c>
+      <c r="B872">
+        <f t="shared" si="13"/>
+        <v>0.91672723561019376</v>
+      </c>
+    </row>
+    <row r="873" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A873">
+        <v>0.872</v>
+      </c>
+      <c r="B873">
+        <f t="shared" si="13"/>
+        <v>0.9174360608737947</v>
+      </c>
+    </row>
+    <row r="874" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A874">
+        <v>0.873</v>
+      </c>
+      <c r="B874">
+        <f t="shared" si="13"/>
+        <v>0.91814462923508688</v>
+      </c>
+    </row>
+    <row r="875" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A875">
+        <v>0.874</v>
+      </c>
+      <c r="B875">
+        <f t="shared" si="13"/>
+        <v>0.9188529410782692</v>
+      </c>
+    </row>
+    <row r="876" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A876">
+        <v>0.875</v>
+      </c>
+      <c r="B876">
+        <f t="shared" si="13"/>
+        <v>0.91956099678653203</v>
+      </c>
+    </row>
+    <row r="877" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A877">
+        <v>0.876</v>
+      </c>
+      <c r="B877">
+        <f t="shared" si="13"/>
+        <v>0.9202687967420603</v>
+      </c>
+    </row>
+    <row r="878" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A878">
+        <v>0.877</v>
+      </c>
+      <c r="B878">
+        <f t="shared" si="13"/>
+        <v>0.92097634132603778</v>
+      </c>
+    </row>
+    <row r="879" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A879">
+        <v>0.878</v>
+      </c>
+      <c r="B879">
+        <f t="shared" si="13"/>
+        <v>0.92168363091865058</v>
+      </c>
+    </row>
+    <row r="880" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A880">
+        <v>0.879</v>
+      </c>
+      <c r="B880">
+        <f t="shared" si="13"/>
+        <v>0.92239066589909091</v>
+      </c>
+    </row>
+    <row r="881" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A881">
+        <v>0.88</v>
+      </c>
+      <c r="B881">
+        <f t="shared" si="13"/>
+        <v>0.92309744664556082</v>
+      </c>
+    </row>
+    <row r="882" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A882">
+        <v>0.88100000000000001</v>
+      </c>
+      <c r="B882">
+        <f t="shared" si="13"/>
+        <v>0.92380397353527577</v>
+      </c>
+    </row>
+    <row r="883" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A883">
+        <v>0.88200000000000001</v>
+      </c>
+      <c r="B883">
+        <f t="shared" si="13"/>
+        <v>0.92451024694446882</v>
+      </c>
+    </row>
+    <row r="884" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A884">
+        <v>0.88300000000000001</v>
+      </c>
+      <c r="B884">
+        <f t="shared" si="13"/>
+        <v>0.92521626724839356</v>
+      </c>
+    </row>
+    <row r="885" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A885">
+        <v>0.88400000000000001</v>
+      </c>
+      <c r="B885">
+        <f t="shared" si="13"/>
+        <v>0.92592203482132818</v>
+      </c>
+    </row>
+    <row r="886" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A886">
+        <v>0.88500000000000001</v>
+      </c>
+      <c r="B886">
+        <f t="shared" si="13"/>
+        <v>0.92662755003657915</v>
+      </c>
+    </row>
+    <row r="887" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A887">
+        <v>0.88600000000000001</v>
+      </c>
+      <c r="B887">
+        <f t="shared" si="13"/>
+        <v>0.92733281326648431</v>
+      </c>
+    </row>
+    <row r="888" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A888">
+        <v>0.88700000000000001</v>
+      </c>
+      <c r="B888">
+        <f t="shared" si="13"/>
+        <v>0.92803782488241737</v>
+      </c>
+    </row>
+    <row r="889" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A889">
+        <v>0.88800000000000001</v>
+      </c>
+      <c r="B889">
+        <f t="shared" si="13"/>
+        <v>0.92874258525479059</v>
+      </c>
+    </row>
+    <row r="890" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A890">
+        <v>0.88900000000000001</v>
+      </c>
+      <c r="B890">
+        <f t="shared" si="13"/>
+        <v>0.92944709475305887</v>
+      </c>
+    </row>
+    <row r="891" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A891">
+        <v>0.89</v>
+      </c>
+      <c r="B891">
+        <f t="shared" si="13"/>
+        <v>0.93015135374572289</v>
+      </c>
+    </row>
+    <row r="892" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A892">
+        <v>0.89100000000000001</v>
+      </c>
+      <c r="B892">
+        <f t="shared" si="13"/>
+        <v>0.93085536260033308</v>
+      </c>
+    </row>
+    <row r="893" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A893">
+        <v>0.89200000000000002</v>
+      </c>
+      <c r="B893">
+        <f t="shared" si="13"/>
+        <v>0.93155912168349297</v>
+      </c>
+    </row>
+    <row r="894" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A894">
+        <v>0.89300000000000002</v>
+      </c>
+      <c r="B894">
+        <f t="shared" si="13"/>
+        <v>0.9322626313608624</v>
+      </c>
+    </row>
+    <row r="895" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A895">
+        <v>0.89400000000000002</v>
+      </c>
+      <c r="B895">
+        <f t="shared" si="13"/>
+        <v>0.93296589199716118</v>
+      </c>
+    </row>
+    <row r="896" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A896">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="B896">
+        <f t="shared" si="13"/>
+        <v>0.93366890395617286</v>
+      </c>
+    </row>
+    <row r="897" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A897">
+        <v>0.89600000000000002</v>
+      </c>
+      <c r="B897">
+        <f t="shared" si="13"/>
+        <v>0.93437166760074752</v>
+      </c>
+    </row>
+    <row r="898" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A898">
+        <v>0.89700000000000002</v>
+      </c>
+      <c r="B898">
+        <f t="shared" si="13"/>
+        <v>0.93507418329280589</v>
+      </c>
+    </row>
+    <row r="899" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A899">
+        <v>0.89800000000000002</v>
+      </c>
+      <c r="B899">
+        <f t="shared" ref="B899:B962" si="14">EXP(LN(A899 + 0.009076778736745) / 1.46927)</f>
+        <v>0.9357764513933422</v>
+      </c>
+    </row>
+    <row r="900" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A900">
+        <v>0.89900000000000002</v>
+      </c>
+      <c r="B900">
+        <f t="shared" si="14"/>
+        <v>0.93647847226242764</v>
+      </c>
+    </row>
+    <row r="901" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A901">
+        <v>0.9</v>
+      </c>
+      <c r="B901">
+        <f t="shared" si="14"/>
+        <v>0.93718024625921426</v>
+      </c>
+    </row>
+    <row r="902" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A902">
+        <v>0.90100000000000002</v>
+      </c>
+      <c r="B902">
+        <f t="shared" si="14"/>
+        <v>0.93788177374193771</v>
+      </c>
+    </row>
+    <row r="903" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A903">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="B903">
+        <f t="shared" si="14"/>
+        <v>0.93858305506792084</v>
+      </c>
+    </row>
+    <row r="904" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A904">
+        <v>0.90300000000000002</v>
+      </c>
+      <c r="B904">
+        <f t="shared" si="14"/>
+        <v>0.93928409059357687</v>
+      </c>
+    </row>
+    <row r="905" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A905">
+        <v>0.90400000000000003</v>
+      </c>
+      <c r="B905">
+        <f t="shared" si="14"/>
+        <v>0.9399848806744131</v>
+      </c>
+    </row>
+    <row r="906" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A906">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="B906">
+        <f t="shared" si="14"/>
+        <v>0.94068542566503377</v>
+      </c>
+    </row>
+    <row r="907" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A907">
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="B907">
+        <f t="shared" si="14"/>
+        <v>0.94138572591914349</v>
+      </c>
+    </row>
+    <row r="908" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A908">
+        <v>0.90700000000000003</v>
+      </c>
+      <c r="B908">
+        <f t="shared" si="14"/>
+        <v>0.94208578178955049</v>
+      </c>
+    </row>
+    <row r="909" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A909">
+        <v>0.90800000000000003</v>
+      </c>
+      <c r="B909">
+        <f t="shared" si="14"/>
+        <v>0.94278559362817005</v>
+      </c>
+    </row>
+    <row r="910" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A910">
+        <v>0.90900000000000003</v>
+      </c>
+      <c r="B910">
+        <f t="shared" si="14"/>
+        <v>0.94348516178602737</v>
+      </c>
+    </row>
+    <row r="911" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A911">
+        <v>0.91</v>
+      </c>
+      <c r="B911">
+        <f t="shared" si="14"/>
+        <v>0.94418448661326115</v>
+      </c>
+    </row>
+    <row r="912" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A912">
+        <v>0.91100000000000003</v>
+      </c>
+      <c r="B912">
+        <f t="shared" si="14"/>
+        <v>0.94488356845912658</v>
+      </c>
+    </row>
+    <row r="913" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A913">
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="B913">
+        <f t="shared" si="14"/>
+        <v>0.94558240767199842</v>
+      </c>
+    </row>
+    <row r="914" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A914">
+        <v>0.91300000000000003</v>
+      </c>
+      <c r="B914">
+        <f t="shared" si="14"/>
+        <v>0.94628100459937459</v>
+      </c>
+    </row>
+    <row r="915" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A915">
+        <v>0.91400000000000003</v>
+      </c>
+      <c r="B915">
+        <f t="shared" si="14"/>
+        <v>0.94697935958787882</v>
+      </c>
+    </row>
+    <row r="916" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A916">
+        <v>0.91500000000000004</v>
+      </c>
+      <c r="B916">
+        <f t="shared" si="14"/>
+        <v>0.94767747298326432</v>
+      </c>
+    </row>
+    <row r="917" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A917">
+        <v>0.91600000000000004</v>
+      </c>
+      <c r="B917">
+        <f t="shared" si="14"/>
+        <v>0.94837534513041633</v>
+      </c>
+    </row>
+    <row r="918" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A918">
+        <v>0.91700000000000004</v>
+      </c>
+      <c r="B918">
+        <f t="shared" si="14"/>
+        <v>0.94907297637335575</v>
+      </c>
+    </row>
+    <row r="919" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A919">
+        <v>0.91800000000000004</v>
+      </c>
+      <c r="B919">
+        <f t="shared" si="14"/>
+        <v>0.94977036705524187</v>
+      </c>
+    </row>
+    <row r="920" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A920">
+        <v>0.91900000000000004</v>
+      </c>
+      <c r="B920">
+        <f t="shared" si="14"/>
+        <v>0.95046751751837566</v>
+      </c>
+    </row>
+    <row r="921" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A921">
+        <v>0.92</v>
+      </c>
+      <c r="B921">
+        <f t="shared" si="14"/>
+        <v>0.95116442810420287</v>
+      </c>
+    </row>
+    <row r="922" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A922">
+        <v>0.92100000000000004</v>
+      </c>
+      <c r="B922">
+        <f t="shared" si="14"/>
+        <v>0.95186109915331685</v>
+      </c>
+    </row>
+    <row r="923" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A923">
+        <v>0.92200000000000004</v>
+      </c>
+      <c r="B923">
+        <f t="shared" si="14"/>
+        <v>0.9525575310054617</v>
+      </c>
+    </row>
+    <row r="924" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A924">
+        <v>0.92300000000000004</v>
+      </c>
+      <c r="B924">
+        <f t="shared" si="14"/>
+        <v>0.95325372399953556</v>
+      </c>
+    </row>
+    <row r="925" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A925">
+        <v>0.92400000000000004</v>
+      </c>
+      <c r="B925">
+        <f t="shared" si="14"/>
+        <v>0.95394967847359324</v>
+      </c>
+    </row>
+    <row r="926" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A926">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="B926">
+        <f t="shared" si="14"/>
+        <v>0.95464539476484933</v>
+      </c>
+    </row>
+    <row r="927" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A927">
+        <v>0.92600000000000005</v>
+      </c>
+      <c r="B927">
+        <f t="shared" si="14"/>
+        <v>0.95534087320968142</v>
+      </c>
+    </row>
+    <row r="928" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A928">
+        <v>0.92700000000000005</v>
+      </c>
+      <c r="B928">
+        <f t="shared" si="14"/>
+        <v>0.95603611414363254</v>
+      </c>
+    </row>
+    <row r="929" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A929">
+        <v>0.92800000000000005</v>
+      </c>
+      <c r="B929">
+        <f t="shared" si="14"/>
+        <v>0.95673111790141485</v>
+      </c>
+    </row>
+    <row r="930" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A930">
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="B930">
+        <f t="shared" si="14"/>
+        <v>0.95742588481691204</v>
+      </c>
+    </row>
+    <row r="931" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A931">
+        <v>0.93</v>
+      </c>
+      <c r="B931">
+        <f t="shared" si="14"/>
+        <v>0.95812041522318236</v>
+      </c>
+    </row>
+    <row r="932" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A932">
+        <v>0.93100000000000005</v>
+      </c>
+      <c r="B932">
+        <f t="shared" si="14"/>
+        <v>0.95881470945246161</v>
+      </c>
+    </row>
+    <row r="933" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A933">
+        <v>0.93200000000000005</v>
+      </c>
+      <c r="B933">
+        <f t="shared" si="14"/>
+        <v>0.95950876783616601</v>
+      </c>
+    </row>
+    <row r="934" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A934">
+        <v>0.93300000000000005</v>
+      </c>
+      <c r="B934">
+        <f t="shared" si="14"/>
+        <v>0.96020259070489522</v>
+      </c>
+    </row>
+    <row r="935" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A935">
+        <v>0.93400000000000005</v>
+      </c>
+      <c r="B935">
+        <f t="shared" si="14"/>
+        <v>0.960896178388435</v>
+      </c>
+    </row>
+    <row r="936" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A936">
+        <v>0.93500000000000005</v>
+      </c>
+      <c r="B936">
+        <f t="shared" si="14"/>
+        <v>0.96158953121576018</v>
+      </c>
+    </row>
+    <row r="937" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A937">
+        <v>0.93600000000000005</v>
+      </c>
+      <c r="B937">
+        <f t="shared" si="14"/>
+        <v>0.96228264951503761</v>
+      </c>
+    </row>
+    <row r="938" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A938">
+        <v>0.93700000000000006</v>
+      </c>
+      <c r="B938">
+        <f t="shared" si="14"/>
+        <v>0.96297553361362864</v>
+      </c>
+    </row>
+    <row r="939" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A939">
+        <v>0.93799999999999994</v>
+      </c>
+      <c r="B939">
+        <f t="shared" si="14"/>
+        <v>0.9636681838380925</v>
+      </c>
+    </row>
+    <row r="940" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A940">
+        <v>0.93899999999999995</v>
+      </c>
+      <c r="B940">
+        <f t="shared" si="14"/>
+        <v>0.96436060051418859</v>
+      </c>
+    </row>
+    <row r="941" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A941">
+        <v>0.94</v>
+      </c>
+      <c r="B941">
+        <f t="shared" si="14"/>
+        <v>0.96505278396687977</v>
+      </c>
+    </row>
+    <row r="942" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A942">
+        <v>0.94099999999999995</v>
+      </c>
+      <c r="B942">
+        <f t="shared" si="14"/>
+        <v>0.96574473452033449</v>
+      </c>
+    </row>
+    <row r="943" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A943">
+        <v>0.94199999999999995</v>
+      </c>
+      <c r="B943">
+        <f t="shared" si="14"/>
+        <v>0.96643645249793042</v>
+      </c>
+    </row>
+    <row r="944" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A944">
+        <v>0.94299999999999995</v>
+      </c>
+      <c r="B944">
+        <f t="shared" si="14"/>
+        <v>0.96712793822225618</v>
+      </c>
+    </row>
+    <row r="945" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A945">
+        <v>0.94399999999999995</v>
+      </c>
+      <c r="B945">
+        <f t="shared" si="14"/>
+        <v>0.96781919201511513</v>
+      </c>
+    </row>
+    <row r="946" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A946">
+        <v>0.94499999999999995</v>
+      </c>
+      <c r="B946">
+        <f t="shared" si="14"/>
+        <v>0.96851021419752747</v>
+      </c>
+    </row>
+    <row r="947" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A947">
+        <v>0.94599999999999995</v>
+      </c>
+      <c r="B947">
+        <f t="shared" si="14"/>
+        <v>0.96920100508973295</v>
+      </c>
+    </row>
+    <row r="948" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A948">
+        <v>0.94699999999999995</v>
+      </c>
+      <c r="B948">
+        <f t="shared" si="14"/>
+        <v>0.96989156501119411</v>
+      </c>
+    </row>
+    <row r="949" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A949">
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="B949">
+        <f t="shared" si="14"/>
+        <v>0.97058189428059827</v>
+      </c>
+    </row>
+    <row r="950" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A950">
+        <v>0.94899999999999995</v>
+      </c>
+      <c r="B950">
+        <f t="shared" si="14"/>
+        <v>0.97127199321586066</v>
+      </c>
+    </row>
+    <row r="951" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A951">
+        <v>0.95</v>
+      </c>
+      <c r="B951">
+        <f t="shared" si="14"/>
+        <v>0.97196186213412727</v>
+      </c>
+    </row>
+    <row r="952" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A952">
+        <v>0.95099999999999996</v>
+      </c>
+      <c r="B952">
+        <f t="shared" si="14"/>
+        <v>0.9726515013517768</v>
+      </c>
+    </row>
+    <row r="953" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A953">
+        <v>0.95199999999999996</v>
+      </c>
+      <c r="B953">
+        <f t="shared" si="14"/>
+        <v>0.97334091118442412</v>
+      </c>
+    </row>
+    <row r="954" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A954">
+        <v>0.95299999999999996</v>
+      </c>
+      <c r="B954">
+        <f t="shared" si="14"/>
+        <v>0.97403009194692236</v>
+      </c>
+    </row>
+    <row r="955" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A955">
+        <v>0.95399999999999996</v>
+      </c>
+      <c r="B955">
+        <f t="shared" si="14"/>
+        <v>0.97471904395336584</v>
+      </c>
+    </row>
+    <row r="956" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A956">
+        <v>0.95499999999999996</v>
+      </c>
+      <c r="B956">
+        <f t="shared" si="14"/>
+        <v>0.97540776751709235</v>
+      </c>
+    </row>
+    <row r="957" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A957">
+        <v>0.95599999999999996</v>
+      </c>
+      <c r="B957">
+        <f t="shared" si="14"/>
+        <v>0.9760962629506863</v>
+      </c>
+    </row>
+    <row r="958" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A958">
+        <v>0.95699999999999996</v>
+      </c>
+      <c r="B958">
+        <f t="shared" si="14"/>
+        <v>0.9767845305659808</v>
+      </c>
+    </row>
+    <row r="959" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A959">
+        <v>0.95799999999999996</v>
+      </c>
+      <c r="B959">
+        <f t="shared" si="14"/>
+        <v>0.97747257067406024</v>
+      </c>
+    </row>
+    <row r="960" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A960">
+        <v>0.95899999999999996</v>
+      </c>
+      <c r="B960">
+        <f t="shared" si="14"/>
+        <v>0.97816038358526336</v>
+      </c>
+    </row>
+    <row r="961" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A961">
+        <v>0.96</v>
+      </c>
+      <c r="B961">
+        <f t="shared" si="14"/>
+        <v>0.97884796960918541</v>
+      </c>
+    </row>
+    <row r="962" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A962">
+        <v>0.96099999999999997</v>
+      </c>
+      <c r="B962">
+        <f t="shared" si="14"/>
+        <v>0.97953532905468066</v>
+      </c>
+    </row>
+    <row r="963" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A963">
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="B963">
+        <f t="shared" ref="B963:B1001" si="15">EXP(LN(A963 + 0.009076778736745) / 1.46927)</f>
+        <v>0.9802224622298652</v>
+      </c>
+    </row>
+    <row r="964" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A964">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="B964">
+        <f t="shared" si="15"/>
+        <v>0.98090936944211915</v>
+      </c>
+    </row>
+    <row r="965" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A965">
+        <v>0.96399999999999997</v>
+      </c>
+      <c r="B965">
+        <f t="shared" si="15"/>
+        <v>0.98159605099808933</v>
+      </c>
+    </row>
+    <row r="966" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A966">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="B966">
+        <f t="shared" si="15"/>
+        <v>0.98228250720369203</v>
+      </c>
+    </row>
+    <row r="967" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A967">
+        <v>0.96599999999999997</v>
+      </c>
+      <c r="B967">
+        <f t="shared" si="15"/>
+        <v>0.98296873836411514</v>
+      </c>
+    </row>
+    <row r="968" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A968">
+        <v>0.96699999999999997</v>
+      </c>
+      <c r="B968">
+        <f t="shared" si="15"/>
+        <v>0.98365474478382042</v>
+      </c>
+    </row>
+    <row r="969" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A969">
+        <v>0.96799999999999997</v>
+      </c>
+      <c r="B969">
+        <f t="shared" si="15"/>
+        <v>0.9843405267665466</v>
+      </c>
+    </row>
+    <row r="970" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A970">
+        <v>0.96899999999999997</v>
+      </c>
+      <c r="B970">
+        <f t="shared" si="15"/>
+        <v>0.98502608461531138</v>
+      </c>
+    </row>
+    <row r="971" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A971">
+        <v>0.97</v>
+      </c>
+      <c r="B971">
+        <f t="shared" si="15"/>
+        <v>0.98571141863241407</v>
+      </c>
+    </row>
+    <row r="972" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A972">
+        <v>0.97099999999999997</v>
+      </c>
+      <c r="B972">
+        <f t="shared" si="15"/>
+        <v>0.98639652911943809</v>
+      </c>
+    </row>
+    <row r="973" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A973">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="B973">
+        <f t="shared" si="15"/>
+        <v>0.98708141637725288</v>
+      </c>
+    </row>
+    <row r="974" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A974">
+        <v>0.97299999999999998</v>
+      </c>
+      <c r="B974">
+        <f t="shared" si="15"/>
+        <v>0.98776608070601701</v>
+      </c>
+    </row>
+    <row r="975" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A975">
+        <v>0.97399999999999998</v>
+      </c>
+      <c r="B975">
+        <f t="shared" si="15"/>
+        <v>0.98845052240518028</v>
+      </c>
+    </row>
+    <row r="976" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A976">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="B976">
+        <f t="shared" si="15"/>
+        <v>0.98913474177348593</v>
+      </c>
+    </row>
+    <row r="977" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A977">
+        <v>0.97599999999999998</v>
+      </c>
+      <c r="B977">
+        <f t="shared" si="15"/>
+        <v>0.98981873910897333</v>
+      </c>
+    </row>
+    <row r="978" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A978">
+        <v>0.97699999999999998</v>
+      </c>
+      <c r="B978">
+        <f t="shared" si="15"/>
+        <v>0.99050251470898021</v>
+      </c>
+    </row>
+    <row r="979" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A979">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="B979">
+        <f t="shared" si="15"/>
+        <v>0.99118606887014504</v>
+      </c>
+    </row>
+    <row r="980" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A980">
+        <v>0.97899999999999998</v>
+      </c>
+      <c r="B980">
+        <f t="shared" si="15"/>
+        <v>0.99186940188840933</v>
+      </c>
+    </row>
+    <row r="981" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A981">
+        <v>0.98</v>
+      </c>
+      <c r="B981">
+        <f t="shared" si="15"/>
+        <v>0.9925525140590199</v>
+      </c>
+    </row>
+    <row r="982" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A982">
+        <v>0.98099999999999998</v>
+      </c>
+      <c r="B982">
+        <f t="shared" si="15"/>
+        <v>0.99323540567653157</v>
+      </c>
+    </row>
+    <row r="983" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A983">
+        <v>0.98199999999999998</v>
+      </c>
+      <c r="B983">
+        <f t="shared" si="15"/>
+        <v>0.99391807703480917</v>
+      </c>
+    </row>
+    <row r="984" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A984">
+        <v>0.98299999999999998</v>
+      </c>
+      <c r="B984">
+        <f t="shared" si="15"/>
+        <v>0.99460052842702984</v>
+      </c>
+    </row>
+    <row r="985" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A985">
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="B985">
+        <f t="shared" si="15"/>
+        <v>0.9952827601456854</v>
+      </c>
+    </row>
+    <row r="986" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A986">
+        <v>0.98499999999999999</v>
+      </c>
+      <c r="B986">
+        <f t="shared" si="15"/>
+        <v>0.99596477248258475</v>
+      </c>
+    </row>
+    <row r="987" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A987">
+        <v>0.98599999999999999</v>
+      </c>
+      <c r="B987">
+        <f t="shared" si="15"/>
+        <v>0.9966465657288559</v>
+      </c>
+    </row>
+    <row r="988" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A988">
+        <v>0.98699999999999999</v>
+      </c>
+      <c r="B988">
+        <f t="shared" si="15"/>
+        <v>0.99732814017494842</v>
+      </c>
+    </row>
+    <row r="989" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A989">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="B989">
+        <f t="shared" si="15"/>
+        <v>0.99800949611063594</v>
+      </c>
+    </row>
+    <row r="990" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A990">
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="B990">
+        <f t="shared" si="15"/>
+        <v>0.99869063382501777</v>
+      </c>
+    </row>
+    <row r="991" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A991">
+        <v>0.99</v>
+      </c>
+      <c r="B991">
+        <f t="shared" si="15"/>
+        <v>0.99937155360652163</v>
+      </c>
+    </row>
+    <row r="992" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A992">
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="B992">
+        <f t="shared" si="15"/>
+        <v>1.0000522557429057</v>
+      </c>
+    </row>
+    <row r="993" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A993">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="B993">
+        <f t="shared" si="15"/>
+        <v>1.0007327405212612</v>
+      </c>
+    </row>
+    <row r="994" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A994">
+        <v>0.99299999999999999</v>
+      </c>
+      <c r="B994">
+        <f t="shared" si="15"/>
+        <v>1.0014130082280137</v>
+      </c>
+    </row>
+    <row r="995" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A995">
+        <v>0.99399999999999999</v>
+      </c>
+      <c r="B995">
+        <f t="shared" si="15"/>
+        <v>1.0020930591489265</v>
+      </c>
+    </row>
+    <row r="996" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A996">
+        <v>0.995</v>
+      </c>
+      <c r="B996">
+        <f t="shared" si="15"/>
+        <v>1.0027728935691023</v>
+      </c>
+    </row>
+    <row r="997" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A997">
+        <v>0.996</v>
+      </c>
+      <c r="B997">
+        <f t="shared" si="15"/>
+        <v>1.0034525117729842</v>
+      </c>
+    </row>
+    <row r="998" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A998">
+        <v>0.997</v>
+      </c>
+      <c r="B998">
+        <f t="shared" si="15"/>
+        <v>1.0041319140443608</v>
+      </c>
+    </row>
+    <row r="999" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A999">
+        <v>0.998</v>
+      </c>
+      <c r="B999">
+        <f t="shared" si="15"/>
+        <v>1.0048111006663649</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A1000">
+        <v>0.999</v>
+      </c>
+      <c r="B1000">
+        <f t="shared" si="15"/>
+        <v>1.0054900719214785</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A1001">
+        <v>1</v>
+      </c>
+      <c r="B1001">
+        <f t="shared" si="15"/>
+        <v>1.0061688280915329</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>